--- a/results/model_results_cc.xlsx
+++ b/results/model_results_cc.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L24"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,6 +477,11 @@
           <t>Time (s)</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Data_norm</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -513,6 +518,7 @@
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -543,8 +549,9 @@
         <v>100</v>
       </c>
       <c r="L3" t="n">
-        <v>13.21178364753723</v>
-      </c>
+        <v>2.347318649291992</v>
+      </c>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -581,6 +588,7 @@
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -611,8 +619,9 @@
         <v>0.01</v>
       </c>
       <c r="L5" t="n">
-        <v>0.744513988494873</v>
-      </c>
+        <v>0.209359884262085</v>
+      </c>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -649,6 +658,7 @@
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -679,8 +689,9 @@
         <v>0.01</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8159894943237305</v>
-      </c>
+        <v>0.2059040069580078</v>
+      </c>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -717,6 +728,7 @@
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -747,8 +759,9 @@
         <v>100</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7551326751708984</v>
-      </c>
+        <v>0.2056839466094971</v>
+      </c>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -785,6 +798,7 @@
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -815,8 +829,9 @@
         <v>0.01</v>
       </c>
       <c r="L11" t="n">
-        <v>0.9605786800384521</v>
-      </c>
+        <v>0.2275722026824951</v>
+      </c>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -853,6 +868,7 @@
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -883,8 +899,9 @@
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>1.049010515213013</v>
-      </c>
+        <v>0.2510108947753906</v>
+      </c>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -921,6 +938,7 @@
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -951,8 +969,9 @@
         <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>1.21029806137085</v>
-      </c>
+        <v>0.2704861164093018</v>
+      </c>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -989,6 +1008,7 @@
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1019,8 +1039,9 @@
         <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>1.381270170211792</v>
-      </c>
+        <v>0.2751548290252686</v>
+      </c>
+      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1057,6 +1078,7 @@
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1093,6 +1115,7 @@
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1129,6 +1152,7 @@
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1165,6 +1189,7 @@
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1201,6 +1226,7 @@
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1237,6 +1263,7 @@
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1273,6 +1300,294 @@
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.6264999999999999</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.2433628318584071</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.3351104341203351</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.2819609099647549</v>
+      </c>
+      <c r="G25" t="n">
+        <v>3319</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1368</v>
+      </c>
+      <c r="I25" t="n">
+        <v>873</v>
+      </c>
+      <c r="J25" t="n">
+        <v>440</v>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="n">
+        <v>0.007625818252563477</v>
+      </c>
+      <c r="M25" t="n">
+        <v>94.59893444466807</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.3087195600942655</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.2993145468392993</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.3039443155452436</v>
+      </c>
+      <c r="G26" t="n">
+        <v>3807</v>
+      </c>
+      <c r="H26" t="n">
+        <v>880</v>
+      </c>
+      <c r="I26" t="n">
+        <v>920</v>
+      </c>
+      <c r="J26" t="n">
+        <v>393</v>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="n">
+        <v>0.008142232894897461</v>
+      </c>
+      <c r="M26" t="n">
+        <v>94.59893444466807</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>5</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.7495000000000001</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.3962882096069869</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.2764661081492765</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.3257065948855989</v>
+      </c>
+      <c r="G27" t="n">
+        <v>4134</v>
+      </c>
+      <c r="H27" t="n">
+        <v>553</v>
+      </c>
+      <c r="I27" t="n">
+        <v>950</v>
+      </c>
+      <c r="J27" t="n">
+        <v>363</v>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="n">
+        <v>0.03449916839599609</v>
+      </c>
+      <c r="M27" t="n">
+        <v>94.59893444466807</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>10</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.7448333333333333</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.3892276422764228</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.2916984006092917</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.3334784501523727</v>
+      </c>
+      <c r="G28" t="n">
+        <v>4086</v>
+      </c>
+      <c r="H28" t="n">
+        <v>601</v>
+      </c>
+      <c r="I28" t="n">
+        <v>930</v>
+      </c>
+      <c r="J28" t="n">
+        <v>383</v>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="n">
+        <v>0.06470394134521484</v>
+      </c>
+      <c r="M28" t="n">
+        <v>94.59893444466807</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>30</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.8038333333333333</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.6422594142259415</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.2338156892612338</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.3428252372975991</v>
+      </c>
+      <c r="G29" t="n">
+        <v>4516</v>
+      </c>
+      <c r="H29" t="n">
+        <v>171</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1006</v>
+      </c>
+      <c r="J29" t="n">
+        <v>307</v>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="n">
+        <v>0.05328202247619629</v>
+      </c>
+      <c r="M29" t="n">
+        <v>94.59893444466807</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>50</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.8075</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.6763392857142857</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.2307692307692308</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.3441226575809199</v>
+      </c>
+      <c r="G30" t="n">
+        <v>4542</v>
+      </c>
+      <c r="H30" t="n">
+        <v>145</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1010</v>
+      </c>
+      <c r="J30" t="n">
+        <v>303</v>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="n">
+        <v>0.03752303123474121</v>
+      </c>
+      <c r="M30" t="n">
+        <v>94.59893444466807</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>100</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.7038724373576309</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.2353389185072353</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.3527397260273973</v>
+      </c>
+      <c r="G31" t="n">
+        <v>4557</v>
+      </c>
+      <c r="H31" t="n">
+        <v>130</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1004</v>
+      </c>
+      <c r="J31" t="n">
+        <v>309</v>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="n">
+        <v>0.01758193969726562</v>
+      </c>
+      <c r="M31" t="n">
+        <v>94.59893444466807</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/model_results_cc.xlsx
+++ b/results/model_results_cc.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,71 +425,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:M61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Epsilon</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Accuracy</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Precision</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Recall</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>F1 Score</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>TN</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>TP</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Best C</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Time (s)</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Data_norm</t>
         </is>
@@ -549,7 +561,7 @@
         <v>100</v>
       </c>
       <c r="L3" t="n">
-        <v>2.347318649291992</v>
+        <v>11.37634587287903</v>
       </c>
       <c r="M3" t="inlineStr"/>
     </row>
@@ -619,7 +631,7 @@
         <v>0.01</v>
       </c>
       <c r="L5" t="n">
-        <v>0.209359884262085</v>
+        <v>0.7431106567382812</v>
       </c>
       <c r="M5" t="inlineStr"/>
     </row>
@@ -689,7 +701,7 @@
         <v>0.01</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2059040069580078</v>
+        <v>0.577608585357666</v>
       </c>
       <c r="M7" t="inlineStr"/>
     </row>
@@ -759,7 +771,7 @@
         <v>100</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2056839466094971</v>
+        <v>0.6926877498626709</v>
       </c>
       <c r="M9" t="inlineStr"/>
     </row>
@@ -829,7 +841,7 @@
         <v>0.01</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2275722026824951</v>
+        <v>0.6948978900909424</v>
       </c>
       <c r="M11" t="inlineStr"/>
     </row>
@@ -899,7 +911,7 @@
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2510108947753906</v>
+        <v>0.9892487525939941</v>
       </c>
       <c r="M13" t="inlineStr"/>
     </row>
@@ -969,7 +981,7 @@
         <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2704861164093018</v>
+        <v>1.154241323471069</v>
       </c>
       <c r="M15" t="inlineStr"/>
     </row>
@@ -1039,7 +1051,7 @@
         <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2751548290252686</v>
+        <v>1.297367095947266</v>
       </c>
       <c r="M17" t="inlineStr"/>
     </row>
@@ -1337,7 +1349,7 @@
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="n">
-        <v>0.007625818252563477</v>
+        <v>0.04477548599243164</v>
       </c>
       <c r="M25" t="n">
         <v>94.59893444466807</v>
@@ -1378,7 +1390,7 @@
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="n">
-        <v>0.008142232894897461</v>
+        <v>0.04774236679077148</v>
       </c>
       <c r="M26" t="n">
         <v>94.59893444466807</v>
@@ -1419,7 +1431,7 @@
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="n">
-        <v>0.03449916839599609</v>
+        <v>0.3922996520996094</v>
       </c>
       <c r="M27" t="n">
         <v>94.59893444466807</v>
@@ -1438,29 +1450,29 @@
         <v>0.7448333333333333</v>
       </c>
       <c r="D28" t="n">
-        <v>0.3892276422764228</v>
+        <v>0.3894523326572008</v>
       </c>
       <c r="E28" t="n">
-        <v>0.2916984006092917</v>
+        <v>0.2924600152322925</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3334784501523727</v>
+        <v>0.3340582862113963</v>
       </c>
       <c r="G28" t="n">
-        <v>4086</v>
+        <v>4085</v>
       </c>
       <c r="H28" t="n">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="I28" t="n">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="J28" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="n">
-        <v>0.06470394134521484</v>
+        <v>0.5104947090148926</v>
       </c>
       <c r="M28" t="n">
         <v>94.59893444466807</v>
@@ -1476,32 +1488,32 @@
         <v>30</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8038333333333333</v>
+        <v>0.8041666666666667</v>
       </c>
       <c r="D29" t="n">
-        <v>0.6422594142259415</v>
+        <v>0.6443514644351465</v>
       </c>
       <c r="E29" t="n">
-        <v>0.2338156892612338</v>
+        <v>0.2345773038842346</v>
       </c>
       <c r="F29" t="n">
-        <v>0.3428252372975991</v>
+        <v>0.3439419318816304</v>
       </c>
       <c r="G29" t="n">
-        <v>4516</v>
+        <v>4517</v>
       </c>
       <c r="H29" t="n">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I29" t="n">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="J29" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="n">
-        <v>0.05328202247619629</v>
+        <v>0.4474050998687744</v>
       </c>
       <c r="M29" t="n">
         <v>94.59893444466807</v>
@@ -1542,7 +1554,7 @@
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="n">
-        <v>0.03752303123474121</v>
+        <v>0.406085729598999</v>
       </c>
       <c r="M30" t="n">
         <v>94.59893444466807</v>
@@ -1583,10 +1595,1116 @@
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="n">
-        <v>0.01758193969726562</v>
+        <v>0.1340081691741943</v>
       </c>
       <c r="M31" t="n">
         <v>94.59893444466807</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.3788214443952149</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.6511805026656512</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.4789915966386555</v>
+      </c>
+      <c r="G32" t="n">
+        <v>3285</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1402</v>
+      </c>
+      <c r="I32" t="n">
+        <v>458</v>
+      </c>
+      <c r="J32" t="n">
+        <v>855</v>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Original_hpt_balanced</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.6736896909551124</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.6854648662053781</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.6421266927326759</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.6630410822962189</v>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L33" t="n">
+        <v>11.31671285629272</v>
+      </c>
+      <c r="M33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Input_balanced</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.7815</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.003046458492003047</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.006065200909780136</v>
+      </c>
+      <c r="G34" t="n">
+        <v>4685</v>
+      </c>
+      <c r="H34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1309</v>
+      </c>
+      <c r="J34" t="n">
+        <v>4</v>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Input_hpt_balanced</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.5081384854191928</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.5081460851623645</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.5084862006516885</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.5082964488644546</v>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.6691312789916992</v>
+      </c>
+      <c r="M35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Input_balanced</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.7641666666666667</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.4430803571428572</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.3023610053313023</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.3594386600271616</v>
+      </c>
+      <c r="G36" t="n">
+        <v>4188</v>
+      </c>
+      <c r="H36" t="n">
+        <v>499</v>
+      </c>
+      <c r="I36" t="n">
+        <v>916</v>
+      </c>
+      <c r="J36" t="n">
+        <v>397</v>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Input_hpt_balanced</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.5356048533892888</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.5362433579448476</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.5272782716607274</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.5316960819243557</v>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.6300170421600342</v>
+      </c>
+      <c r="M37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Input_balanced</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>5</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.664</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.3488172043010753</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.6176694592536177</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.445849367784497</v>
+      </c>
+      <c r="G38" t="n">
+        <v>3173</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1514</v>
+      </c>
+      <c r="I38" t="n">
+        <v>502</v>
+      </c>
+      <c r="J38" t="n">
+        <v>811</v>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Input_hpt_balanced</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>5</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.606146233757299</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.6135390865028315</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.5740211196608742</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.593069433382045</v>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.7419569492340088</v>
+      </c>
+      <c r="M39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Input_balanced</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>10</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.6171666666666666</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.323402727925341</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.6862147753236862</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.4396194193705782</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2802</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1885</v>
+      </c>
+      <c r="I40" t="n">
+        <v>412</v>
+      </c>
+      <c r="J40" t="n">
+        <v>901</v>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Input_hpt_balanced</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>10</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.6329179315405805</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.6431027056280418</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.5973656050254104</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.6193659787311537</v>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="n">
+        <v>1</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.8864743709564209</v>
+      </c>
+      <c r="M41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Input_balanced</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>30</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.6315</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.3361313868613139</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.7014470677837015</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.4544781643227239</v>
+      </c>
+      <c r="G42" t="n">
+        <v>2868</v>
+      </c>
+      <c r="H42" t="n">
+        <v>1819</v>
+      </c>
+      <c r="I42" t="n">
+        <v>392</v>
+      </c>
+      <c r="J42" t="n">
+        <v>921</v>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Input_hpt_balanced</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>30</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.6598488242764061</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.6724847914784746</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.6233872373662244</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.6469647822692931</v>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L43" t="n">
+        <v>1.090618848800659</v>
+      </c>
+      <c r="M43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Input_balanced</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>50</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0.3529181355268312</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.6862147753236862</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.4661148473874806</v>
+      </c>
+      <c r="G44" t="n">
+        <v>3035</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1652</v>
+      </c>
+      <c r="I44" t="n">
+        <v>412</v>
+      </c>
+      <c r="J44" t="n">
+        <v>901</v>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Input_hpt_balanced</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>50</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0.6647480715151828</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0.6765549441926344</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.631685856800579</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.6532930646019943</v>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="n">
+        <v>10</v>
+      </c>
+      <c r="L45" t="n">
+        <v>1.241770505905151</v>
+      </c>
+      <c r="M45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Input_balanced</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>100</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0.6758333333333333</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0.3676716917922948</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.6686976389946687</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.4744663604431235</v>
+      </c>
+      <c r="G46" t="n">
+        <v>3177</v>
+      </c>
+      <c r="H46" t="n">
+        <v>1510</v>
+      </c>
+      <c r="I46" t="n">
+        <v>435</v>
+      </c>
+      <c r="J46" t="n">
+        <v>878</v>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Input_hpt_balanced</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>100</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0.6697544424665112</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0.6810647790985545</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.6387001384350531</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.6591550622532798</v>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L47" t="n">
+        <v>1.690831184387207</v>
+      </c>
+      <c r="M47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Output_balanced</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0.6895</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.3782108060230293</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.6504188880426505</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.4782973956874825</v>
+      </c>
+      <c r="G48" t="n">
+        <v>3283</v>
+      </c>
+      <c r="H48" t="n">
+        <v>1404</v>
+      </c>
+      <c r="I48" t="n">
+        <v>459</v>
+      </c>
+      <c r="J48" t="n">
+        <v>854</v>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Output_balanced</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.6896666666666667</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0.3783783783783784</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.6504188880426505</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.4784313725490196</v>
+      </c>
+      <c r="G49" t="n">
+        <v>3284</v>
+      </c>
+      <c r="H49" t="n">
+        <v>1403</v>
+      </c>
+      <c r="I49" t="n">
+        <v>459</v>
+      </c>
+      <c r="J49" t="n">
+        <v>854</v>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Output_balanced</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>5</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0.6898333333333333</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.3786536758193091</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.6511805026656512</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.4788574628955475</v>
+      </c>
+      <c r="G50" t="n">
+        <v>3284</v>
+      </c>
+      <c r="H50" t="n">
+        <v>1403</v>
+      </c>
+      <c r="I50" t="n">
+        <v>458</v>
+      </c>
+      <c r="J50" t="n">
+        <v>855</v>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Output_balanced</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>10</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0.3788214443952149</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.6511805026656512</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.4789915966386555</v>
+      </c>
+      <c r="G51" t="n">
+        <v>3285</v>
+      </c>
+      <c r="H51" t="n">
+        <v>1402</v>
+      </c>
+      <c r="I51" t="n">
+        <v>458</v>
+      </c>
+      <c r="J51" t="n">
+        <v>855</v>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Output_balanced</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>30</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0.3788214443952149</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.6511805026656512</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.4789915966386555</v>
+      </c>
+      <c r="G52" t="n">
+        <v>3285</v>
+      </c>
+      <c r="H52" t="n">
+        <v>1402</v>
+      </c>
+      <c r="I52" t="n">
+        <v>458</v>
+      </c>
+      <c r="J52" t="n">
+        <v>855</v>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Output_balanced</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>50</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0.3788214443952149</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.6511805026656512</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.4789915966386555</v>
+      </c>
+      <c r="G53" t="n">
+        <v>3285</v>
+      </c>
+      <c r="H53" t="n">
+        <v>1402</v>
+      </c>
+      <c r="I53" t="n">
+        <v>458</v>
+      </c>
+      <c r="J53" t="n">
+        <v>855</v>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Output_balanced</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>100</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0.3788214443952149</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.6511805026656512</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.4789915966386555</v>
+      </c>
+      <c r="G54" t="n">
+        <v>3285</v>
+      </c>
+      <c r="H54" t="n">
+        <v>1402</v>
+      </c>
+      <c r="I54" t="n">
+        <v>458</v>
+      </c>
+      <c r="J54" t="n">
+        <v>855</v>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Internal_balanced</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0.5941666666666666</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0.2385834109972041</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.38994668697639</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.296039317721885</v>
+      </c>
+      <c r="G55" t="n">
+        <v>3053</v>
+      </c>
+      <c r="H55" t="n">
+        <v>1634</v>
+      </c>
+      <c r="I55" t="n">
+        <v>801</v>
+      </c>
+      <c r="J55" t="n">
+        <v>512</v>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="n">
+        <v>0.06237244606018066</v>
+      </c>
+      <c r="M55" t="n">
+        <v>108.3506938566066</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Internal_balanced</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0.5946666666666667</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0.2646192679848549</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.479055597867479</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.3409214092140921</v>
+      </c>
+      <c r="G56" t="n">
+        <v>2939</v>
+      </c>
+      <c r="H56" t="n">
+        <v>1748</v>
+      </c>
+      <c r="I56" t="n">
+        <v>684</v>
+      </c>
+      <c r="J56" t="n">
+        <v>629</v>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="n">
+        <v>0.2387123107910156</v>
+      </c>
+      <c r="M56" t="n">
+        <v>108.3506938566066</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Internal_balanced</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>5</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0.6396666666666667</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0.323785803237858</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.594059405940594</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.4191295002686727</v>
+      </c>
+      <c r="G57" t="n">
+        <v>3058</v>
+      </c>
+      <c r="H57" t="n">
+        <v>1629</v>
+      </c>
+      <c r="I57" t="n">
+        <v>533</v>
+      </c>
+      <c r="J57" t="n">
+        <v>780</v>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="n">
+        <v>0.5375761985778809</v>
+      </c>
+      <c r="M57" t="n">
+        <v>108.3506938566066</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Internal_balanced</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>10</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0.6476666666666666</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0.3329161451814768</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.6077684691546078</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.430188679245283</v>
+      </c>
+      <c r="G58" t="n">
+        <v>3088</v>
+      </c>
+      <c r="H58" t="n">
+        <v>1599</v>
+      </c>
+      <c r="I58" t="n">
+        <v>515</v>
+      </c>
+      <c r="J58" t="n">
+        <v>798</v>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="n">
+        <v>1.088827848434448</v>
+      </c>
+      <c r="M58" t="n">
+        <v>108.3506938566066</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Internal_balanced</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>30</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0.6888333333333333</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0.375673249551167</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.6374714394516374</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.4727478113527252</v>
+      </c>
+      <c r="G59" t="n">
+        <v>3296</v>
+      </c>
+      <c r="H59" t="n">
+        <v>1391</v>
+      </c>
+      <c r="I59" t="n">
+        <v>476</v>
+      </c>
+      <c r="J59" t="n">
+        <v>837</v>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="n">
+        <v>0.6548721790313721</v>
+      </c>
+      <c r="M59" t="n">
+        <v>108.3506938566066</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Internal_balanced</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>50</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0.3745002221235006</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.642041127189642</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.4730639730639731</v>
+      </c>
+      <c r="G60" t="n">
+        <v>3279</v>
+      </c>
+      <c r="H60" t="n">
+        <v>1408</v>
+      </c>
+      <c r="I60" t="n">
+        <v>470</v>
+      </c>
+      <c r="J60" t="n">
+        <v>843</v>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="n">
+        <v>0.2520732879638672</v>
+      </c>
+      <c r="M60" t="n">
+        <v>108.3506938566066</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Internal_balanced</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>100</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0.6905</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0.3787878787878788</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.6473724295506473</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.4779308405960079</v>
+      </c>
+      <c r="G61" t="n">
+        <v>3293</v>
+      </c>
+      <c r="H61" t="n">
+        <v>1394</v>
+      </c>
+      <c r="I61" t="n">
+        <v>463</v>
+      </c>
+      <c r="J61" t="n">
+        <v>850</v>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="n">
+        <v>0.190861701965332</v>
+      </c>
+      <c r="M61" t="n">
+        <v>108.3506938566066</v>
       </c>
     </row>
   </sheetData>

--- a/results/model_results_cc.xlsx
+++ b/results/model_results_cc.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:N54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,55 +429,60 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>Row_ID</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>Accuracy</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Precision</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Recall</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>F1 Score</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>TN</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>TP</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Best C</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Time (s)</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Data_norm</t>
         </is>
@@ -486,1106 +491,1978 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Original</t>
+          <t>Original_oversampled</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>0</v>
       </c>
-      <c r="C2" t="n">
-        <v>0.8108333333333333</v>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.6977777777777778</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2391469916222392</v>
+        <v>0.3788214443952149</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3562110039705048</v>
+        <v>0.6511805026656512</v>
       </c>
       <c r="G2" t="n">
-        <v>4551</v>
+        <v>0.4789915966386555</v>
       </c>
       <c r="H2" t="n">
-        <v>136</v>
+        <v>3285</v>
       </c>
       <c r="I2" t="n">
-        <v>999</v>
+        <v>1402</v>
       </c>
       <c r="J2" t="n">
-        <v>314</v>
-      </c>
-      <c r="K2" t="inlineStr"/>
+        <v>458</v>
+      </c>
+      <c r="K2" t="n">
+        <v>855</v>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Original_hpt</t>
+          <t>Original</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>0</v>
       </c>
-      <c r="C3" t="n">
-        <v>0.8102083333333333</v>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.7126792406855361</v>
+        <v>0.8108333333333333</v>
       </c>
       <c r="E3" t="n">
-        <v>0.24253022330686</v>
+        <v>0.6977777777777778</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3614996034679863</v>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+        <v>0.2391469916222392</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.3562110039705048</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4551</v>
+      </c>
+      <c r="I3" t="n">
+        <v>136</v>
+      </c>
+      <c r="J3" t="n">
+        <v>999</v>
+      </c>
       <c r="K3" t="n">
-        <v>100</v>
-      </c>
-      <c r="L3" t="n">
-        <v>2.347318649291992</v>
-      </c>
+        <v>314</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Original_hpt_oversampled</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.7811666666666667</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>0.6736896909551124</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>0.6854648662053781</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>0.6421266927326759</v>
       </c>
       <c r="G4" t="n">
-        <v>4687</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1313</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
+        <v>0.6630410822962189</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M4" t="n">
+        <v>4.856741666793823</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Input_hpt</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>0.1</v>
       </c>
-      <c r="C5" t="n">
-        <v>0.7782083333333334</v>
-      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>0.7815</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+        <v>0.003046458492003047</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.006065200909780136</v>
+      </c>
+      <c r="H5" t="n">
+        <v>4685</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1309</v>
+      </c>
       <c r="K5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.209359884262085</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Input_hpt_oversampled</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.7811666666666667</v>
-      </c>
+        <v>0.1</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>0.5081384854191928</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>0.5081460851623645</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>0.5084862006516885</v>
       </c>
       <c r="G6" t="n">
-        <v>4687</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1313</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
+        <v>0.5082964488644546</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.2756969928741455</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Input_hpt</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
-      <c r="C7" t="n">
-        <v>0.7782083333333334</v>
-      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>0.7641666666666667</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>0.4430803571428572</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+        <v>0.3023610053313023</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.3594386600271616</v>
+      </c>
+      <c r="H7" t="n">
+        <v>4188</v>
+      </c>
+      <c r="I7" t="n">
+        <v>499</v>
+      </c>
+      <c r="J7" t="n">
+        <v>916</v>
+      </c>
       <c r="K7" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.2059040069580078</v>
-      </c>
+        <v>397</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Input_hpt_oversampled</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.7831666666666667</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.5356048533892888</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02132520944402132</v>
+        <v>0.5362433579448476</v>
       </c>
       <c r="F8" t="n">
-        <v>0.04126750184229919</v>
+        <v>0.5272782716607274</v>
       </c>
       <c r="G8" t="n">
-        <v>4671</v>
-      </c>
-      <c r="H8" t="n">
-        <v>16</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1285</v>
-      </c>
-      <c r="J8" t="n">
-        <v>28</v>
-      </c>
+        <v>0.5316960819243557</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.2700321674346924</v>
+      </c>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Input_hpt</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>5</v>
       </c>
-      <c r="C9" t="n">
-        <v>0.7809583333333333</v>
-      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.5783236383389382</v>
+        <v>0.664</v>
       </c>
       <c r="E9" t="n">
-        <v>0.04471391894370071</v>
+        <v>0.3488172043010753</v>
       </c>
       <c r="F9" t="n">
-        <v>0.08297648756437934</v>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+        <v>0.6176694592536177</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.445849367784497</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3173</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1514</v>
+      </c>
+      <c r="J9" t="n">
+        <v>502</v>
+      </c>
       <c r="K9" t="n">
-        <v>100</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.2056839466094971</v>
-      </c>
+        <v>811</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Input_hpt_oversampled</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.7961666666666667</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.67578125</v>
+        <v>0.606146233757299</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1317593297791318</v>
+        <v>0.6135390865028315</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2205226258763544</v>
+        <v>0.5740211196608742</v>
       </c>
       <c r="G10" t="n">
-        <v>4604</v>
-      </c>
-      <c r="H10" t="n">
-        <v>83</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1140</v>
-      </c>
-      <c r="J10" t="n">
-        <v>173</v>
-      </c>
+        <v>0.593069433382045</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="L10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.3052220344543457</v>
+      </c>
+      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Input_hpt</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>10</v>
       </c>
-      <c r="C11" t="n">
-        <v>0.7909166666666667</v>
-      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6520083336347747</v>
+        <v>0.6171666666666666</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1232419698401727</v>
+        <v>0.323402727925341</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2072479500188648</v>
-      </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+        <v>0.6862147753236862</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.4396194193705782</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2802</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1885</v>
+      </c>
+      <c r="J11" t="n">
+        <v>412</v>
+      </c>
       <c r="K11" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.2275722026824951</v>
-      </c>
+        <v>901</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Input_hpt_oversampled</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>30</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.8106666666666666</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6911447084233261</v>
+        <v>0.6329179315405805</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2437166793602437</v>
+        <v>0.6431027056280418</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3603603603603603</v>
+        <v>0.5973656050254104</v>
       </c>
       <c r="G12" t="n">
-        <v>4544</v>
-      </c>
-      <c r="H12" t="n">
-        <v>143</v>
-      </c>
-      <c r="I12" t="n">
-        <v>993</v>
-      </c>
-      <c r="J12" t="n">
-        <v>320</v>
-      </c>
+        <v>0.6193659787311537</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.4181919097900391</v>
+      </c>
+      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Input_hpt</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>30</v>
       </c>
-      <c r="C13" t="n">
-        <v>0.8052499999999998</v>
-      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6937228380734474</v>
+        <v>0.6315</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2188576506933375</v>
+        <v>0.3361313868613139</v>
       </c>
       <c r="F13" t="n">
-        <v>0.332430360332738</v>
-      </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+        <v>0.7014470677837015</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.4544781643227239</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2868</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1819</v>
+      </c>
+      <c r="J13" t="n">
+        <v>392</v>
+      </c>
       <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0.2510108947753906</v>
-      </c>
+        <v>921</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Input_hpt_oversampled</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>50</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0.8110000000000001</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6916488222698073</v>
+        <v>0.6598488242764061</v>
       </c>
       <c r="E14" t="n">
-        <v>0.246001523229246</v>
+        <v>0.6724847914784746</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3629213483146068</v>
+        <v>0.6233872373662244</v>
       </c>
       <c r="G14" t="n">
-        <v>4543</v>
-      </c>
-      <c r="H14" t="n">
-        <v>144</v>
-      </c>
-      <c r="I14" t="n">
-        <v>990</v>
-      </c>
-      <c r="J14" t="n">
-        <v>323</v>
-      </c>
+        <v>0.6469647822692931</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="L14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.4509868621826172</v>
+      </c>
+      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Input_hpt</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>50</v>
       </c>
-      <c r="C15" t="n">
-        <v>0.8083333333333333</v>
-      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.7104435415548893</v>
+        <v>0.656</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2314452877033108</v>
+        <v>0.3529181355268312</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3487893215793864</v>
-      </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+        <v>0.6862147753236862</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.4661148473874806</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3035</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1652</v>
+      </c>
+      <c r="J15" t="n">
+        <v>412</v>
+      </c>
       <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.2704861164093018</v>
-      </c>
+        <v>901</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Original_hpt</t>
         </is>
       </c>
       <c r="B16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="n">
+        <v>0.8102083333333333</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.7126792406855361</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.24253022330686</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.3614996034679863</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="n">
         <v>100</v>
       </c>
-      <c r="C16" t="n">
-        <v>0.8113333333333334</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.6937901498929336</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.2467631378522468</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.3640449438202247</v>
-      </c>
-      <c r="G16" t="n">
-        <v>4544</v>
-      </c>
-      <c r="H16" t="n">
-        <v>143</v>
-      </c>
-      <c r="I16" t="n">
-        <v>989</v>
-      </c>
-      <c r="J16" t="n">
-        <v>324</v>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+      <c r="M16" t="n">
+        <v>4.584688901901245</v>
+      </c>
+      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Input_hpt</t>
+          <t>Input_hpt_oversampled</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>100</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0.810125</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.7142392384934356</v>
+        <v>0.6647480715151828</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2406515820508119</v>
+        <v>0.6765549441926344</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3595968749758223</v>
-      </c>
-      <c r="G17" t="inlineStr"/>
+        <v>0.631685856800579</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.6532930646019943</v>
+      </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
-        <v>0.2751548290252686</v>
-      </c>
-      <c r="M17" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.4298820495605469</v>
+      </c>
+      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Output</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0.8105</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6973094170403588</v>
+        <v>0.6758333333333333</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2368621477532369</v>
+        <v>0.3676716917922948</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3536100056850483</v>
+        <v>0.6686976389946687</v>
       </c>
       <c r="G18" t="n">
-        <v>4552</v>
+        <v>0.4744663604431235</v>
       </c>
       <c r="H18" t="n">
-        <v>135</v>
+        <v>3177</v>
       </c>
       <c r="I18" t="n">
-        <v>1002</v>
+        <v>1510</v>
       </c>
       <c r="J18" t="n">
-        <v>311</v>
-      </c>
-      <c r="K18" t="inlineStr"/>
+        <v>435</v>
+      </c>
+      <c r="K18" t="n">
+        <v>878</v>
+      </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Output</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0.8110000000000001</v>
-      </c>
+        <v>0.1</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.6984478935698448</v>
+        <v>0.7811666666666667</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2399086062452399</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3571428571428572</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>4551</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>136</v>
+        <v>4687</v>
       </c>
       <c r="I19" t="n">
-        <v>998</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>315</v>
-      </c>
-      <c r="K19" t="inlineStr"/>
+        <v>1313</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Output</t>
+          <t>Input_hpt</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0.8108333333333333</v>
-      </c>
+        <v>0.1</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.6977777777777778</v>
+        <v>0.7782083333333334</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2391469916222392</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3562110039705048</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>4551</v>
-      </c>
-      <c r="H20" t="n">
-        <v>136</v>
-      </c>
-      <c r="I20" t="n">
-        <v>999</v>
-      </c>
-      <c r="J20" t="n">
-        <v>314</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
+      <c r="L20" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.2275252342224121</v>
+      </c>
+      <c r="N20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Output</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0.8108333333333333</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.6977777777777778</v>
+        <v>0.7811666666666667</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2391469916222392</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3562110039705048</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>4551</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>136</v>
+        <v>4687</v>
       </c>
       <c r="I21" t="n">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>314</v>
-      </c>
-      <c r="K21" t="inlineStr"/>
+        <v>1313</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Output</t>
+          <t>Input_hpt_oversampled</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>30</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0.8108333333333333</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="n">
-        <v>0.6977777777777778</v>
+        <v>0.6697544424665112</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2391469916222392</v>
+        <v>0.6810647790985545</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3562110039705048</v>
+        <v>0.6387001384350531</v>
       </c>
       <c r="G22" t="n">
-        <v>4551</v>
-      </c>
-      <c r="H22" t="n">
-        <v>136</v>
-      </c>
-      <c r="I22" t="n">
-        <v>999</v>
-      </c>
-      <c r="J22" t="n">
-        <v>314</v>
-      </c>
+        <v>0.6591550622532798</v>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
+      <c r="L22" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.6873941421508789</v>
+      </c>
+      <c r="N22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Output</t>
+          <t>Output_oversampled</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>50</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0.8108333333333333</v>
-      </c>
+        <v>0.1</v>
+      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="n">
-        <v>0.6977777777777778</v>
+        <v>0.6895</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2391469916222392</v>
+        <v>0.3782108060230293</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3562110039705048</v>
+        <v>0.6504188880426505</v>
       </c>
       <c r="G23" t="n">
-        <v>4551</v>
+        <v>0.4782973956874825</v>
       </c>
       <c r="H23" t="n">
-        <v>136</v>
+        <v>3283</v>
       </c>
       <c r="I23" t="n">
-        <v>999</v>
+        <v>1404</v>
       </c>
       <c r="J23" t="n">
-        <v>314</v>
-      </c>
-      <c r="K23" t="inlineStr"/>
+        <v>459</v>
+      </c>
+      <c r="K23" t="n">
+        <v>854</v>
+      </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Output</t>
+          <t>Output_oversampled</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>100</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0.8108333333333333</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="n">
-        <v>0.6977777777777778</v>
+        <v>0.6896666666666667</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2391469916222392</v>
+        <v>0.3783783783783784</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3562110039705048</v>
+        <v>0.6504188880426505</v>
       </c>
       <c r="G24" t="n">
-        <v>4551</v>
+        <v>0.4784313725490196</v>
       </c>
       <c r="H24" t="n">
-        <v>136</v>
+        <v>3284</v>
       </c>
       <c r="I24" t="n">
-        <v>999</v>
+        <v>1403</v>
       </c>
       <c r="J24" t="n">
-        <v>314</v>
-      </c>
-      <c r="K24" t="inlineStr"/>
+        <v>459</v>
+      </c>
+      <c r="K24" t="n">
+        <v>854</v>
+      </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Output_oversampled</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C25" t="n">
-        <v>0.6264999999999999</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="n">
-        <v>0.2433628318584071</v>
+        <v>0.6898333333333333</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3351104341203351</v>
+        <v>0.3786536758193091</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2819609099647549</v>
+        <v>0.6511805026656512</v>
       </c>
       <c r="G25" t="n">
-        <v>3319</v>
+        <v>0.4788574628955475</v>
       </c>
       <c r="H25" t="n">
-        <v>1368</v>
+        <v>3284</v>
       </c>
       <c r="I25" t="n">
-        <v>873</v>
+        <v>1403</v>
       </c>
       <c r="J25" t="n">
-        <v>440</v>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="n">
-        <v>0.007625818252563477</v>
-      </c>
-      <c r="M25" t="n">
-        <v>94.59893444466807</v>
-      </c>
+        <v>458</v>
+      </c>
+      <c r="K25" t="n">
+        <v>855</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Output_oversampled</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0.7</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="n">
-        <v>0.3087195600942655</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2993145468392993</v>
+        <v>0.3788214443952149</v>
       </c>
       <c r="F26" t="n">
-        <v>0.3039443155452436</v>
+        <v>0.6511805026656512</v>
       </c>
       <c r="G26" t="n">
-        <v>3807</v>
+        <v>0.4789915966386555</v>
       </c>
       <c r="H26" t="n">
-        <v>880</v>
+        <v>3285</v>
       </c>
       <c r="I26" t="n">
-        <v>920</v>
+        <v>1402</v>
       </c>
       <c r="J26" t="n">
-        <v>393</v>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="n">
-        <v>0.008142232894897461</v>
-      </c>
-      <c r="M26" t="n">
-        <v>94.59893444466807</v>
-      </c>
+        <v>458</v>
+      </c>
+      <c r="K26" t="n">
+        <v>855</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Output_oversampled</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5</v>
-      </c>
-      <c r="C27" t="n">
-        <v>0.7495000000000001</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="n">
-        <v>0.3962882096069869</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2764661081492765</v>
+        <v>0.3788214443952149</v>
       </c>
       <c r="F27" t="n">
-        <v>0.3257065948855989</v>
+        <v>0.6511805026656512</v>
       </c>
       <c r="G27" t="n">
-        <v>4134</v>
+        <v>0.4789915966386555</v>
       </c>
       <c r="H27" t="n">
-        <v>553</v>
+        <v>3285</v>
       </c>
       <c r="I27" t="n">
-        <v>950</v>
+        <v>1402</v>
       </c>
       <c r="J27" t="n">
-        <v>363</v>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="n">
-        <v>0.03449916839599609</v>
-      </c>
-      <c r="M27" t="n">
-        <v>94.59893444466807</v>
-      </c>
+        <v>458</v>
+      </c>
+      <c r="K27" t="n">
+        <v>855</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Output_oversampled</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>10</v>
-      </c>
-      <c r="C28" t="n">
-        <v>0.7448333333333333</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="n">
-        <v>0.3892276422764228</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>0.2916984006092917</v>
+        <v>0.3788214443952149</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3334784501523727</v>
+        <v>0.6511805026656512</v>
       </c>
       <c r="G28" t="n">
-        <v>4086</v>
+        <v>0.4789915966386555</v>
       </c>
       <c r="H28" t="n">
-        <v>601</v>
+        <v>3285</v>
       </c>
       <c r="I28" t="n">
-        <v>930</v>
+        <v>1402</v>
       </c>
       <c r="J28" t="n">
-        <v>383</v>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="n">
-        <v>0.06470394134521484</v>
-      </c>
-      <c r="M28" t="n">
-        <v>94.59893444466807</v>
-      </c>
+        <v>458</v>
+      </c>
+      <c r="K28" t="n">
+        <v>855</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Input_hpt</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>30</v>
-      </c>
-      <c r="C29" t="n">
-        <v>0.8038333333333333</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="n">
-        <v>0.6422594142259415</v>
+        <v>0.7782083333333334</v>
       </c>
       <c r="E29" t="n">
-        <v>0.2338156892612338</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>0.3428252372975991</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>4516</v>
-      </c>
-      <c r="H29" t="n">
-        <v>171</v>
-      </c>
-      <c r="I29" t="n">
-        <v>1006</v>
-      </c>
-      <c r="J29" t="n">
-        <v>307</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="n">
-        <v>0.05328202247619629</v>
+        <v>0.01</v>
       </c>
       <c r="M29" t="n">
-        <v>94.59893444466807</v>
-      </c>
+        <v>0.3279678821563721</v>
+      </c>
+      <c r="N29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Output_oversampled</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>50</v>
-      </c>
-      <c r="C30" t="n">
-        <v>0.8075</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="n">
-        <v>0.6763392857142857</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>0.2307692307692308</v>
+        <v>0.3788214443952149</v>
       </c>
       <c r="F30" t="n">
-        <v>0.3441226575809199</v>
+        <v>0.6511805026656512</v>
       </c>
       <c r="G30" t="n">
-        <v>4542</v>
+        <v>0.4789915966386555</v>
       </c>
       <c r="H30" t="n">
-        <v>145</v>
+        <v>3285</v>
       </c>
       <c r="I30" t="n">
-        <v>1010</v>
+        <v>1402</v>
       </c>
       <c r="J30" t="n">
-        <v>303</v>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="n">
-        <v>0.03752303123474121</v>
-      </c>
-      <c r="M30" t="n">
-        <v>94.59893444466807</v>
-      </c>
+        <v>458</v>
+      </c>
+      <c r="K30" t="n">
+        <v>855</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>5</v>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="n">
+        <v>0.7831666666666667</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.02132520944402132</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.04126750184229919</v>
+      </c>
+      <c r="H31" t="n">
+        <v>4671</v>
+      </c>
+      <c r="I31" t="n">
+        <v>16</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1285</v>
+      </c>
+      <c r="K31" t="n">
+        <v>28</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Input_hpt</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>5</v>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="n">
+        <v>0.7809583333333333</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.5783236383389382</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.04471391894370071</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.08297648756437934</v>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="n">
+        <v>100</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.2482380867004395</v>
+      </c>
+      <c r="N32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>10</v>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>0.7961666666666667</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.67578125</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.1317593297791318</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.2205226258763544</v>
+      </c>
+      <c r="H33" t="n">
+        <v>4604</v>
+      </c>
+      <c r="I33" t="n">
+        <v>83</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1140</v>
+      </c>
+      <c r="K33" t="n">
+        <v>173</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Input_hpt</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>10</v>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>0.7909166666666667</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.6520083336347747</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.1232419698401727</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.2072479500188648</v>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.2551002502441406</v>
+      </c>
+      <c r="N34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>30</v>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="n">
+        <v>0.8106666666666666</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.6911447084233261</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.2437166793602437</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.3603603603603603</v>
+      </c>
+      <c r="H35" t="n">
+        <v>4544</v>
+      </c>
+      <c r="I35" t="n">
+        <v>143</v>
+      </c>
+      <c r="J35" t="n">
+        <v>993</v>
+      </c>
+      <c r="K35" t="n">
+        <v>320</v>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Input_hpt</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>30</v>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="n">
+        <v>0.8052499999999998</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.6937228380734474</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.2188576506933375</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.332430360332738</v>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="n">
+        <v>1</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.3003261089324951</v>
+      </c>
+      <c r="N36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>50</v>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="n">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.6916488222698073</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.246001523229246</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.3629213483146068</v>
+      </c>
+      <c r="H37" t="n">
+        <v>4543</v>
+      </c>
+      <c r="I37" t="n">
+        <v>144</v>
+      </c>
+      <c r="J37" t="n">
+        <v>990</v>
+      </c>
+      <c r="K37" t="n">
+        <v>323</v>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Input_hpt</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>50</v>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="n">
+        <v>0.8083333333333333</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.7104435415548893</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.2314452877033108</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.3487893215793864</v>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="n">
+        <v>1</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.3467190265655518</v>
+      </c>
+      <c r="N38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>100</v>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="n">
+        <v>0.8113333333333334</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.6937901498929336</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.2467631378522468</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.3640449438202247</v>
+      </c>
+      <c r="H39" t="n">
+        <v>4544</v>
+      </c>
+      <c r="I39" t="n">
+        <v>143</v>
+      </c>
+      <c r="J39" t="n">
+        <v>989</v>
+      </c>
+      <c r="K39" t="n">
+        <v>324</v>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Input_hpt</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>100</v>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="n">
+        <v>0.810125</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.7142392384934356</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.2406515820508119</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.3595968749758223</v>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="n">
+        <v>1</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.322206974029541</v>
+      </c>
+      <c r="N40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="n">
+        <v>0.8105</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.6973094170403588</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.2368621477532369</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.3536100056850483</v>
+      </c>
+      <c r="H41" t="n">
+        <v>4552</v>
+      </c>
+      <c r="I41" t="n">
+        <v>135</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1002</v>
+      </c>
+      <c r="K41" t="n">
+        <v>311</v>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="n">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.6984478935698448</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.2399086062452399</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.3571428571428572</v>
+      </c>
+      <c r="H42" t="n">
+        <v>4551</v>
+      </c>
+      <c r="I42" t="n">
+        <v>136</v>
+      </c>
+      <c r="J42" t="n">
+        <v>998</v>
+      </c>
+      <c r="K42" t="n">
+        <v>315</v>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>5</v>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="n">
+        <v>0.8108333333333333</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.6977777777777778</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.2391469916222392</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.3562110039705048</v>
+      </c>
+      <c r="H43" t="n">
+        <v>4551</v>
+      </c>
+      <c r="I43" t="n">
+        <v>136</v>
+      </c>
+      <c r="J43" t="n">
+        <v>999</v>
+      </c>
+      <c r="K43" t="n">
+        <v>314</v>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>10</v>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="n">
+        <v>0.8108333333333333</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.6977777777777778</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.2391469916222392</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.3562110039705048</v>
+      </c>
+      <c r="H44" t="n">
+        <v>4551</v>
+      </c>
+      <c r="I44" t="n">
+        <v>136</v>
+      </c>
+      <c r="J44" t="n">
+        <v>999</v>
+      </c>
+      <c r="K44" t="n">
+        <v>314</v>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>30</v>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="n">
+        <v>0.8108333333333333</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.6977777777777778</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.2391469916222392</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.3562110039705048</v>
+      </c>
+      <c r="H45" t="n">
+        <v>4551</v>
+      </c>
+      <c r="I45" t="n">
+        <v>136</v>
+      </c>
+      <c r="J45" t="n">
+        <v>999</v>
+      </c>
+      <c r="K45" t="n">
+        <v>314</v>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>50</v>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="n">
+        <v>0.8108333333333333</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.6977777777777778</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.2391469916222392</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.3562110039705048</v>
+      </c>
+      <c r="H46" t="n">
+        <v>4551</v>
+      </c>
+      <c r="I46" t="n">
+        <v>136</v>
+      </c>
+      <c r="J46" t="n">
+        <v>999</v>
+      </c>
+      <c r="K46" t="n">
+        <v>314</v>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>100</v>
+      </c>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="n">
+        <v>0.8108333333333333</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.6977777777777778</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.2391469916222392</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.3562110039705048</v>
+      </c>
+      <c r="H47" t="n">
+        <v>4551</v>
+      </c>
+      <c r="I47" t="n">
+        <v>136</v>
+      </c>
+      <c r="J47" t="n">
+        <v>999</v>
+      </c>
+      <c r="K47" t="n">
+        <v>314</v>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>Internal</t>
         </is>
       </c>
-      <c r="B31" t="n">
+      <c r="B48" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="n">
+        <v>0.6264999999999999</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.2433628318584071</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.3351104341203351</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.2819609099647549</v>
+      </c>
+      <c r="H48" t="n">
+        <v>3319</v>
+      </c>
+      <c r="I48" t="n">
+        <v>1368</v>
+      </c>
+      <c r="J48" t="n">
+        <v>873</v>
+      </c>
+      <c r="K48" t="n">
+        <v>440</v>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="n">
+        <v>0.008665800094604492</v>
+      </c>
+      <c r="N48" t="n">
+        <v>94.59893444466807</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.3087195600942655</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.2993145468392993</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.3039443155452436</v>
+      </c>
+      <c r="H49" t="n">
+        <v>3807</v>
+      </c>
+      <c r="I49" t="n">
+        <v>880</v>
+      </c>
+      <c r="J49" t="n">
+        <v>920</v>
+      </c>
+      <c r="K49" t="n">
+        <v>393</v>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="n">
+        <v>0.0115962028503418</v>
+      </c>
+      <c r="N49" t="n">
+        <v>94.59893444466807</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>5</v>
+      </c>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="n">
+        <v>0.7495000000000001</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.3962882096069869</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.2764661081492765</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.3257065948855989</v>
+      </c>
+      <c r="H50" t="n">
+        <v>4134</v>
+      </c>
+      <c r="I50" t="n">
+        <v>553</v>
+      </c>
+      <c r="J50" t="n">
+        <v>950</v>
+      </c>
+      <c r="K50" t="n">
+        <v>363</v>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="n">
+        <v>0.05359697341918945</v>
+      </c>
+      <c r="N50" t="n">
+        <v>94.59893444466807</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>10</v>
+      </c>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="n">
+        <v>0.7448333333333333</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.3892276422764228</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.2916984006092917</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.3334784501523727</v>
+      </c>
+      <c r="H51" t="n">
+        <v>4086</v>
+      </c>
+      <c r="I51" t="n">
+        <v>601</v>
+      </c>
+      <c r="J51" t="n">
+        <v>930</v>
+      </c>
+      <c r="K51" t="n">
+        <v>383</v>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="n">
+        <v>0.2166001796722412</v>
+      </c>
+      <c r="N51" t="n">
+        <v>94.59893444466807</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>30</v>
+      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="n">
+        <v>0.8038333333333333</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.6422594142259415</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.2338156892612338</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.3428252372975991</v>
+      </c>
+      <c r="H52" t="n">
+        <v>4516</v>
+      </c>
+      <c r="I52" t="n">
+        <v>171</v>
+      </c>
+      <c r="J52" t="n">
+        <v>1006</v>
+      </c>
+      <c r="K52" t="n">
+        <v>307</v>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="n">
+        <v>0.2572116851806641</v>
+      </c>
+      <c r="N52" t="n">
+        <v>94.59893444466807</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>50</v>
+      </c>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="n">
+        <v>0.8075</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.6763392857142857</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.2307692307692308</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.3441226575809199</v>
+      </c>
+      <c r="H53" t="n">
+        <v>4542</v>
+      </c>
+      <c r="I53" t="n">
+        <v>145</v>
+      </c>
+      <c r="J53" t="n">
+        <v>1010</v>
+      </c>
+      <c r="K53" t="n">
+        <v>303</v>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="n">
+        <v>0.145618200302124</v>
+      </c>
+      <c r="N53" t="n">
+        <v>94.59893444466807</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
         <v>100</v>
       </c>
-      <c r="C31" t="n">
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="n">
         <v>0.8110000000000001</v>
       </c>
-      <c r="D31" t="n">
+      <c r="E54" t="n">
         <v>0.7038724373576309</v>
       </c>
-      <c r="E31" t="n">
+      <c r="F54" t="n">
         <v>0.2353389185072353</v>
       </c>
-      <c r="F31" t="n">
+      <c r="G54" t="n">
         <v>0.3527397260273973</v>
       </c>
-      <c r="G31" t="n">
+      <c r="H54" t="n">
         <v>4557</v>
       </c>
-      <c r="H31" t="n">
+      <c r="I54" t="n">
         <v>130</v>
       </c>
-      <c r="I31" t="n">
+      <c r="J54" t="n">
         <v>1004</v>
       </c>
-      <c r="J31" t="n">
+      <c r="K54" t="n">
         <v>309</v>
       </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="n">
-        <v>0.01758193969726562</v>
-      </c>
-      <c r="M31" t="n">
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="n">
+        <v>0.03465890884399414</v>
+      </c>
+      <c r="N54" t="n">
         <v>94.59893444466807</v>
       </c>
     </row>

--- a/results/model_results_cc.xlsx
+++ b/results/model_results_cc.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N54"/>
+  <dimension ref="A1:N144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2466,6 +2466,3414 @@
         <v>94.59893444466807</v>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>0</v>
+      </c>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="n">
+        <v>0.8108333333333333</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.6977777777777778</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.2391469916222392</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.3562110039705048</v>
+      </c>
+      <c r="H55" t="n">
+        <v>4551</v>
+      </c>
+      <c r="I55" t="n">
+        <v>136</v>
+      </c>
+      <c r="J55" t="n">
+        <v>999</v>
+      </c>
+      <c r="K55" t="n">
+        <v>314</v>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Original_hpt</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="n">
+        <v>0.8102083333333333</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.7126792406855361</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.24253022330686</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.3614996034679863</v>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="n">
+        <v>100</v>
+      </c>
+      <c r="M56" t="n">
+        <v>2.519381046295166</v>
+      </c>
+      <c r="N56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="n">
+        <v>0.7811666666666667</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>4687</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
+        <v>1313</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Input_hpt</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="n">
+        <v>0.7782083333333334</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0.1984531879425049</v>
+      </c>
+      <c r="N58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="n">
+        <v>0.7811666666666667</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>4687</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="n">
+        <v>1313</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Input_hpt</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="n">
+        <v>0.7782083333333334</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0.1994791030883789</v>
+      </c>
+      <c r="N60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>5</v>
+      </c>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="n">
+        <v>0.7831666666666667</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.02132520944402132</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.04126750184229919</v>
+      </c>
+      <c r="H61" t="n">
+        <v>4671</v>
+      </c>
+      <c r="I61" t="n">
+        <v>16</v>
+      </c>
+      <c r="J61" t="n">
+        <v>1285</v>
+      </c>
+      <c r="K61" t="n">
+        <v>28</v>
+      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Input_hpt</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>5</v>
+      </c>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="n">
+        <v>0.7809583333333333</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.5783236383389382</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.04471391894370071</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0.08297648756437934</v>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="n">
+        <v>100</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0.2199392318725586</v>
+      </c>
+      <c r="N62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>10</v>
+      </c>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="n">
+        <v>0.7961666666666667</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.67578125</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.1317593297791318</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0.2205226258763544</v>
+      </c>
+      <c r="H63" t="n">
+        <v>4604</v>
+      </c>
+      <c r="I63" t="n">
+        <v>83</v>
+      </c>
+      <c r="J63" t="n">
+        <v>1140</v>
+      </c>
+      <c r="K63" t="n">
+        <v>173</v>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Input_hpt</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>10</v>
+      </c>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="n">
+        <v>0.7909166666666667</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.6520083336347747</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.1232419698401727</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0.2072479500188648</v>
+      </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0.2160420417785645</v>
+      </c>
+      <c r="N64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>30</v>
+      </c>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="n">
+        <v>0.8106666666666666</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.6911447084233261</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.2437166793602437</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0.3603603603603603</v>
+      </c>
+      <c r="H65" t="n">
+        <v>4544</v>
+      </c>
+      <c r="I65" t="n">
+        <v>143</v>
+      </c>
+      <c r="J65" t="n">
+        <v>993</v>
+      </c>
+      <c r="K65" t="n">
+        <v>320</v>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Input_hpt</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>30</v>
+      </c>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="n">
+        <v>0.8052499999999998</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.6937228380734474</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0.2188576506933375</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0.332430360332738</v>
+      </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="n">
+        <v>1</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0.2460362911224365</v>
+      </c>
+      <c r="N66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>50</v>
+      </c>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="n">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.6916488222698073</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0.246001523229246</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0.3629213483146068</v>
+      </c>
+      <c r="H67" t="n">
+        <v>4543</v>
+      </c>
+      <c r="I67" t="n">
+        <v>144</v>
+      </c>
+      <c r="J67" t="n">
+        <v>990</v>
+      </c>
+      <c r="K67" t="n">
+        <v>323</v>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Input_hpt</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>50</v>
+      </c>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="n">
+        <v>0.8083333333333333</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.7104435415548893</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0.2314452877033108</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0.3487893215793864</v>
+      </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="n">
+        <v>1</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0.2662069797515869</v>
+      </c>
+      <c r="N68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>100</v>
+      </c>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="n">
+        <v>0.8113333333333334</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.6937901498929336</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.2467631378522468</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0.3640449438202247</v>
+      </c>
+      <c r="H69" t="n">
+        <v>4544</v>
+      </c>
+      <c r="I69" t="n">
+        <v>143</v>
+      </c>
+      <c r="J69" t="n">
+        <v>989</v>
+      </c>
+      <c r="K69" t="n">
+        <v>324</v>
+      </c>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Input_hpt</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>100</v>
+      </c>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="n">
+        <v>0.810125</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.7142392384934356</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0.2406515820508119</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0.3595968749758223</v>
+      </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="n">
+        <v>1</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0.2772741317749023</v>
+      </c>
+      <c r="N70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="n">
+        <v>0.8105</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0.6973094170403588</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0.2368621477532369</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0.3536100056850483</v>
+      </c>
+      <c r="H71" t="n">
+        <v>4552</v>
+      </c>
+      <c r="I71" t="n">
+        <v>135</v>
+      </c>
+      <c r="J71" t="n">
+        <v>1002</v>
+      </c>
+      <c r="K71" t="n">
+        <v>311</v>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>1</v>
+      </c>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="n">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.6984478935698448</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0.2399086062452399</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0.3571428571428572</v>
+      </c>
+      <c r="H72" t="n">
+        <v>4551</v>
+      </c>
+      <c r="I72" t="n">
+        <v>136</v>
+      </c>
+      <c r="J72" t="n">
+        <v>998</v>
+      </c>
+      <c r="K72" t="n">
+        <v>315</v>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>5</v>
+      </c>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="n">
+        <v>0.8108333333333333</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.6977777777777778</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.2391469916222392</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0.3562110039705048</v>
+      </c>
+      <c r="H73" t="n">
+        <v>4551</v>
+      </c>
+      <c r="I73" t="n">
+        <v>136</v>
+      </c>
+      <c r="J73" t="n">
+        <v>999</v>
+      </c>
+      <c r="K73" t="n">
+        <v>314</v>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>10</v>
+      </c>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="n">
+        <v>0.8108333333333333</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.6977777777777778</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0.2391469916222392</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0.3562110039705048</v>
+      </c>
+      <c r="H74" t="n">
+        <v>4551</v>
+      </c>
+      <c r="I74" t="n">
+        <v>136</v>
+      </c>
+      <c r="J74" t="n">
+        <v>999</v>
+      </c>
+      <c r="K74" t="n">
+        <v>314</v>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>30</v>
+      </c>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="n">
+        <v>0.8108333333333333</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.6977777777777778</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0.2391469916222392</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0.3562110039705048</v>
+      </c>
+      <c r="H75" t="n">
+        <v>4551</v>
+      </c>
+      <c r="I75" t="n">
+        <v>136</v>
+      </c>
+      <c r="J75" t="n">
+        <v>999</v>
+      </c>
+      <c r="K75" t="n">
+        <v>314</v>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>50</v>
+      </c>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="n">
+        <v>0.8108333333333333</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.6977777777777778</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0.2391469916222392</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0.3562110039705048</v>
+      </c>
+      <c r="H76" t="n">
+        <v>4551</v>
+      </c>
+      <c r="I76" t="n">
+        <v>136</v>
+      </c>
+      <c r="J76" t="n">
+        <v>999</v>
+      </c>
+      <c r="K76" t="n">
+        <v>314</v>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>100</v>
+      </c>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="n">
+        <v>0.8108333333333333</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.6977777777777778</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0.2391469916222392</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0.3562110039705048</v>
+      </c>
+      <c r="H77" t="n">
+        <v>4551</v>
+      </c>
+      <c r="I77" t="n">
+        <v>136</v>
+      </c>
+      <c r="J77" t="n">
+        <v>999</v>
+      </c>
+      <c r="K77" t="n">
+        <v>314</v>
+      </c>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="n">
+        <v>0.6264999999999999</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.2433628318584071</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0.3351104341203351</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0.2819609099647549</v>
+      </c>
+      <c r="H78" t="n">
+        <v>3319</v>
+      </c>
+      <c r="I78" t="n">
+        <v>1368</v>
+      </c>
+      <c r="J78" t="n">
+        <v>873</v>
+      </c>
+      <c r="K78" t="n">
+        <v>440</v>
+      </c>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="n">
+        <v>0.009376287460327148</v>
+      </c>
+      <c r="N78" t="n">
+        <v>94.59893444466807</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>1</v>
+      </c>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.3087195600942655</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0.2993145468392993</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0.3039443155452436</v>
+      </c>
+      <c r="H79" t="n">
+        <v>3807</v>
+      </c>
+      <c r="I79" t="n">
+        <v>880</v>
+      </c>
+      <c r="J79" t="n">
+        <v>920</v>
+      </c>
+      <c r="K79" t="n">
+        <v>393</v>
+      </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="n">
+        <v>0.02006101608276367</v>
+      </c>
+      <c r="N79" t="n">
+        <v>94.59893444466807</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>5</v>
+      </c>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="n">
+        <v>0.7495000000000001</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.3962882096069869</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.2764661081492765</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0.3257065948855989</v>
+      </c>
+      <c r="H80" t="n">
+        <v>4134</v>
+      </c>
+      <c r="I80" t="n">
+        <v>553</v>
+      </c>
+      <c r="J80" t="n">
+        <v>950</v>
+      </c>
+      <c r="K80" t="n">
+        <v>363</v>
+      </c>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="n">
+        <v>0.03937602043151855</v>
+      </c>
+      <c r="N80" t="n">
+        <v>94.59893444466807</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>10</v>
+      </c>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="n">
+        <v>0.7448333333333333</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0.3892276422764228</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0.2916984006092917</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0.3334784501523727</v>
+      </c>
+      <c r="H81" t="n">
+        <v>4086</v>
+      </c>
+      <c r="I81" t="n">
+        <v>601</v>
+      </c>
+      <c r="J81" t="n">
+        <v>930</v>
+      </c>
+      <c r="K81" t="n">
+        <v>383</v>
+      </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="n">
+        <v>0.06213283538818359</v>
+      </c>
+      <c r="N81" t="n">
+        <v>94.59893444466807</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>30</v>
+      </c>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="n">
+        <v>0.8038333333333333</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0.6422594142259415</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0.2338156892612338</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0.3428252372975991</v>
+      </c>
+      <c r="H82" t="n">
+        <v>4516</v>
+      </c>
+      <c r="I82" t="n">
+        <v>171</v>
+      </c>
+      <c r="J82" t="n">
+        <v>1006</v>
+      </c>
+      <c r="K82" t="n">
+        <v>307</v>
+      </c>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="n">
+        <v>0.05182099342346191</v>
+      </c>
+      <c r="N82" t="n">
+        <v>94.59893444466807</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>50</v>
+      </c>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="n">
+        <v>0.8075</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0.6763392857142857</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0.2307692307692308</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0.3441226575809199</v>
+      </c>
+      <c r="H83" t="n">
+        <v>4542</v>
+      </c>
+      <c r="I83" t="n">
+        <v>145</v>
+      </c>
+      <c r="J83" t="n">
+        <v>1010</v>
+      </c>
+      <c r="K83" t="n">
+        <v>303</v>
+      </c>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="n">
+        <v>0.04228401184082031</v>
+      </c>
+      <c r="N83" t="n">
+        <v>94.59893444466807</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>100</v>
+      </c>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="n">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0.7038724373576309</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0.2353389185072353</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0.3527397260273973</v>
+      </c>
+      <c r="H84" t="n">
+        <v>4557</v>
+      </c>
+      <c r="I84" t="n">
+        <v>130</v>
+      </c>
+      <c r="J84" t="n">
+        <v>1004</v>
+      </c>
+      <c r="K84" t="n">
+        <v>309</v>
+      </c>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="n">
+        <v>0.01769018173217773</v>
+      </c>
+      <c r="N84" t="n">
+        <v>94.59893444466807</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0.3788214443952149</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0.6511805026656512</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0.4789915966386555</v>
+      </c>
+      <c r="H85" t="n">
+        <v>3285</v>
+      </c>
+      <c r="I85" t="n">
+        <v>1402</v>
+      </c>
+      <c r="J85" t="n">
+        <v>458</v>
+      </c>
+      <c r="K85" t="n">
+        <v>855</v>
+      </c>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Original_hpt_balanced</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>0</v>
+      </c>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" t="n">
+        <v>0.6736896909551124</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0.6854648662053781</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0.6421266927326759</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0.6630410822962189</v>
+      </c>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M86" t="n">
+        <v>2.706584692001343</v>
+      </c>
+      <c r="N86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Input_balanced</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="n">
+        <v>0.7815</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0.003046458492003047</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0.006065200909780136</v>
+      </c>
+      <c r="H87" t="n">
+        <v>4685</v>
+      </c>
+      <c r="I87" t="n">
+        <v>2</v>
+      </c>
+      <c r="J87" t="n">
+        <v>1309</v>
+      </c>
+      <c r="K87" t="n">
+        <v>4</v>
+      </c>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Input_hpt_balanced</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" t="n">
+        <v>0.5081384854191928</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0.5081460851623645</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0.5084862006516885</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0.5082964488644546</v>
+      </c>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0.2221066951751709</v>
+      </c>
+      <c r="N88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Input_balanced</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>1</v>
+      </c>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" t="n">
+        <v>0.7641666666666667</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0.4430803571428572</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0.3023610053313023</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0.3594386600271616</v>
+      </c>
+      <c r="H89" t="n">
+        <v>4188</v>
+      </c>
+      <c r="I89" t="n">
+        <v>499</v>
+      </c>
+      <c r="J89" t="n">
+        <v>916</v>
+      </c>
+      <c r="K89" t="n">
+        <v>397</v>
+      </c>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Input_hpt_balanced</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>1</v>
+      </c>
+      <c r="C90" t="inlineStr"/>
+      <c r="D90" t="n">
+        <v>0.5356048533892888</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0.5362433579448476</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0.5272782716607274</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0.5316960819243557</v>
+      </c>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0.2204828262329102</v>
+      </c>
+      <c r="N90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Input_balanced</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>5</v>
+      </c>
+      <c r="C91" t="inlineStr"/>
+      <c r="D91" t="n">
+        <v>0.664</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0.3488172043010753</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0.6176694592536177</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0.445849367784497</v>
+      </c>
+      <c r="H91" t="n">
+        <v>3173</v>
+      </c>
+      <c r="I91" t="n">
+        <v>1514</v>
+      </c>
+      <c r="J91" t="n">
+        <v>502</v>
+      </c>
+      <c r="K91" t="n">
+        <v>811</v>
+      </c>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Input_hpt_balanced</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>5</v>
+      </c>
+      <c r="C92" t="inlineStr"/>
+      <c r="D92" t="n">
+        <v>0.606146233757299</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0.6135390865028315</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0.5740211196608742</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0.593069433382045</v>
+      </c>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M92" t="n">
+        <v>0.2478330135345459</v>
+      </c>
+      <c r="N92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Input_balanced</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>10</v>
+      </c>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="n">
+        <v>0.6171666666666666</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0.323402727925341</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0.6862147753236862</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0.4396194193705782</v>
+      </c>
+      <c r="H93" t="n">
+        <v>2802</v>
+      </c>
+      <c r="I93" t="n">
+        <v>1885</v>
+      </c>
+      <c r="J93" t="n">
+        <v>412</v>
+      </c>
+      <c r="K93" t="n">
+        <v>901</v>
+      </c>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Input_hpt_balanced</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>10</v>
+      </c>
+      <c r="C94" t="inlineStr"/>
+      <c r="D94" t="n">
+        <v>0.6329179315405805</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0.6431027056280418</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0.5973656050254104</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0.6193659787311537</v>
+      </c>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="n">
+        <v>1</v>
+      </c>
+      <c r="M94" t="n">
+        <v>0.2642927169799805</v>
+      </c>
+      <c r="N94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Input_balanced</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>30</v>
+      </c>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="n">
+        <v>0.6315</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0.3361313868613139</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0.7014470677837015</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0.4544781643227239</v>
+      </c>
+      <c r="H95" t="n">
+        <v>2868</v>
+      </c>
+      <c r="I95" t="n">
+        <v>1819</v>
+      </c>
+      <c r="J95" t="n">
+        <v>392</v>
+      </c>
+      <c r="K95" t="n">
+        <v>921</v>
+      </c>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Input_hpt_balanced</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>30</v>
+      </c>
+      <c r="C96" t="inlineStr"/>
+      <c r="D96" t="n">
+        <v>0.6598488242764061</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0.6724847914784746</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0.6233872373662244</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0.6469647822692931</v>
+      </c>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0.3067100048065186</v>
+      </c>
+      <c r="N96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Input_balanced</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>50</v>
+      </c>
+      <c r="C97" t="inlineStr"/>
+      <c r="D97" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0.3529181355268312</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0.6862147753236862</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0.4661148473874806</v>
+      </c>
+      <c r="H97" t="n">
+        <v>3035</v>
+      </c>
+      <c r="I97" t="n">
+        <v>1652</v>
+      </c>
+      <c r="J97" t="n">
+        <v>412</v>
+      </c>
+      <c r="K97" t="n">
+        <v>901</v>
+      </c>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Input_hpt_balanced</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>50</v>
+      </c>
+      <c r="C98" t="inlineStr"/>
+      <c r="D98" t="n">
+        <v>0.6647480715151828</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0.6765549441926344</v>
+      </c>
+      <c r="F98" t="n">
+        <v>0.631685856800579</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0.6532930646019943</v>
+      </c>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="n">
+        <v>10</v>
+      </c>
+      <c r="M98" t="n">
+        <v>0.343311071395874</v>
+      </c>
+      <c r="N98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Input_balanced</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>100</v>
+      </c>
+      <c r="C99" t="inlineStr"/>
+      <c r="D99" t="n">
+        <v>0.6758333333333333</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0.3676716917922948</v>
+      </c>
+      <c r="F99" t="n">
+        <v>0.6686976389946687</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0.4744663604431235</v>
+      </c>
+      <c r="H99" t="n">
+        <v>3177</v>
+      </c>
+      <c r="I99" t="n">
+        <v>1510</v>
+      </c>
+      <c r="J99" t="n">
+        <v>435</v>
+      </c>
+      <c r="K99" t="n">
+        <v>878</v>
+      </c>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Input_hpt_balanced</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>100</v>
+      </c>
+      <c r="C100" t="inlineStr"/>
+      <c r="D100" t="n">
+        <v>0.6697544424665112</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0.6810647790985545</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0.6387001384350531</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0.6591550622532798</v>
+      </c>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M100" t="n">
+        <v>0.4109749794006348</v>
+      </c>
+      <c r="N100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Output_balanced</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C101" t="inlineStr"/>
+      <c r="D101" t="n">
+        <v>0.6895</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0.3782108060230293</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0.6504188880426505</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0.4782973956874825</v>
+      </c>
+      <c r="H101" t="n">
+        <v>3283</v>
+      </c>
+      <c r="I101" t="n">
+        <v>1404</v>
+      </c>
+      <c r="J101" t="n">
+        <v>459</v>
+      </c>
+      <c r="K101" t="n">
+        <v>854</v>
+      </c>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Output_balanced</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>1</v>
+      </c>
+      <c r="C102" t="inlineStr"/>
+      <c r="D102" t="n">
+        <v>0.6896666666666667</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0.3783783783783784</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0.6504188880426505</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0.4784313725490196</v>
+      </c>
+      <c r="H102" t="n">
+        <v>3284</v>
+      </c>
+      <c r="I102" t="n">
+        <v>1403</v>
+      </c>
+      <c r="J102" t="n">
+        <v>459</v>
+      </c>
+      <c r="K102" t="n">
+        <v>854</v>
+      </c>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Output_balanced</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>5</v>
+      </c>
+      <c r="C103" t="inlineStr"/>
+      <c r="D103" t="n">
+        <v>0.6898333333333333</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0.3786536758193091</v>
+      </c>
+      <c r="F103" t="n">
+        <v>0.6511805026656512</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0.4788574628955475</v>
+      </c>
+      <c r="H103" t="n">
+        <v>3284</v>
+      </c>
+      <c r="I103" t="n">
+        <v>1403</v>
+      </c>
+      <c r="J103" t="n">
+        <v>458</v>
+      </c>
+      <c r="K103" t="n">
+        <v>855</v>
+      </c>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Output_balanced</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>10</v>
+      </c>
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0.3788214443952149</v>
+      </c>
+      <c r="F104" t="n">
+        <v>0.6511805026656512</v>
+      </c>
+      <c r="G104" t="n">
+        <v>0.4789915966386555</v>
+      </c>
+      <c r="H104" t="n">
+        <v>3285</v>
+      </c>
+      <c r="I104" t="n">
+        <v>1402</v>
+      </c>
+      <c r="J104" t="n">
+        <v>458</v>
+      </c>
+      <c r="K104" t="n">
+        <v>855</v>
+      </c>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Output_balanced</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>30</v>
+      </c>
+      <c r="C105" t="inlineStr"/>
+      <c r="D105" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="E105" t="n">
+        <v>0.3788214443952149</v>
+      </c>
+      <c r="F105" t="n">
+        <v>0.6511805026656512</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0.4789915966386555</v>
+      </c>
+      <c r="H105" t="n">
+        <v>3285</v>
+      </c>
+      <c r="I105" t="n">
+        <v>1402</v>
+      </c>
+      <c r="J105" t="n">
+        <v>458</v>
+      </c>
+      <c r="K105" t="n">
+        <v>855</v>
+      </c>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Output_balanced</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>50</v>
+      </c>
+      <c r="C106" t="inlineStr"/>
+      <c r="D106" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="E106" t="n">
+        <v>0.3788214443952149</v>
+      </c>
+      <c r="F106" t="n">
+        <v>0.6511805026656512</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0.4789915966386555</v>
+      </c>
+      <c r="H106" t="n">
+        <v>3285</v>
+      </c>
+      <c r="I106" t="n">
+        <v>1402</v>
+      </c>
+      <c r="J106" t="n">
+        <v>458</v>
+      </c>
+      <c r="K106" t="n">
+        <v>855</v>
+      </c>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Output_balanced</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>100</v>
+      </c>
+      <c r="C107" t="inlineStr"/>
+      <c r="D107" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0.3788214443952149</v>
+      </c>
+      <c r="F107" t="n">
+        <v>0.6511805026656512</v>
+      </c>
+      <c r="G107" t="n">
+        <v>0.4789915966386555</v>
+      </c>
+      <c r="H107" t="n">
+        <v>3285</v>
+      </c>
+      <c r="I107" t="n">
+        <v>1402</v>
+      </c>
+      <c r="J107" t="n">
+        <v>458</v>
+      </c>
+      <c r="K107" t="n">
+        <v>855</v>
+      </c>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Internal_balanced</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C108" t="inlineStr"/>
+      <c r="D108" t="n">
+        <v>0.5941666666666666</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0.2385834109972041</v>
+      </c>
+      <c r="F108" t="n">
+        <v>0.38994668697639</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0.296039317721885</v>
+      </c>
+      <c r="H108" t="n">
+        <v>3053</v>
+      </c>
+      <c r="I108" t="n">
+        <v>1634</v>
+      </c>
+      <c r="J108" t="n">
+        <v>801</v>
+      </c>
+      <c r="K108" t="n">
+        <v>512</v>
+      </c>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="n">
+        <v>0.01076579093933105</v>
+      </c>
+      <c r="N108" t="n">
+        <v>108.3506938566066</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Internal_balanced</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>1</v>
+      </c>
+      <c r="C109" t="inlineStr"/>
+      <c r="D109" t="n">
+        <v>0.5946666666666667</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0.2646192679848549</v>
+      </c>
+      <c r="F109" t="n">
+        <v>0.479055597867479</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0.3409214092140921</v>
+      </c>
+      <c r="H109" t="n">
+        <v>2939</v>
+      </c>
+      <c r="I109" t="n">
+        <v>1748</v>
+      </c>
+      <c r="J109" t="n">
+        <v>684</v>
+      </c>
+      <c r="K109" t="n">
+        <v>629</v>
+      </c>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="n">
+        <v>0.01876688003540039</v>
+      </c>
+      <c r="N109" t="n">
+        <v>108.3506938566066</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Internal_balanced</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>5</v>
+      </c>
+      <c r="C110" t="inlineStr"/>
+      <c r="D110" t="n">
+        <v>0.6396666666666667</v>
+      </c>
+      <c r="E110" t="n">
+        <v>0.323785803237858</v>
+      </c>
+      <c r="F110" t="n">
+        <v>0.594059405940594</v>
+      </c>
+      <c r="G110" t="n">
+        <v>0.4191295002686727</v>
+      </c>
+      <c r="H110" t="n">
+        <v>3058</v>
+      </c>
+      <c r="I110" t="n">
+        <v>1629</v>
+      </c>
+      <c r="J110" t="n">
+        <v>533</v>
+      </c>
+      <c r="K110" t="n">
+        <v>780</v>
+      </c>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="n">
+        <v>0.08148097991943359</v>
+      </c>
+      <c r="N110" t="n">
+        <v>108.3506938566066</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Internal_balanced</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>10</v>
+      </c>
+      <c r="C111" t="inlineStr"/>
+      <c r="D111" t="n">
+        <v>0.6475</v>
+      </c>
+      <c r="E111" t="n">
+        <v>0.3330557868442964</v>
+      </c>
+      <c r="F111" t="n">
+        <v>0.6092916984006093</v>
+      </c>
+      <c r="G111" t="n">
+        <v>0.4306864064602961</v>
+      </c>
+      <c r="H111" t="n">
+        <v>3085</v>
+      </c>
+      <c r="I111" t="n">
+        <v>1602</v>
+      </c>
+      <c r="J111" t="n">
+        <v>513</v>
+      </c>
+      <c r="K111" t="n">
+        <v>800</v>
+      </c>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="n">
+        <v>0.1606519222259521</v>
+      </c>
+      <c r="N111" t="n">
+        <v>108.3506938566066</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Internal_balanced</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>30</v>
+      </c>
+      <c r="C112" t="inlineStr"/>
+      <c r="D112" t="n">
+        <v>0.6888333333333333</v>
+      </c>
+      <c r="E112" t="n">
+        <v>0.375673249551167</v>
+      </c>
+      <c r="F112" t="n">
+        <v>0.6374714394516374</v>
+      </c>
+      <c r="G112" t="n">
+        <v>0.4727478113527252</v>
+      </c>
+      <c r="H112" t="n">
+        <v>3296</v>
+      </c>
+      <c r="I112" t="n">
+        <v>1391</v>
+      </c>
+      <c r="J112" t="n">
+        <v>476</v>
+      </c>
+      <c r="K112" t="n">
+        <v>837</v>
+      </c>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="n">
+        <v>0.1026580333709717</v>
+      </c>
+      <c r="N112" t="n">
+        <v>108.3506938566066</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Internal_balanced</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>50</v>
+      </c>
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="n">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="E113" t="n">
+        <v>0.3745002221235006</v>
+      </c>
+      <c r="F113" t="n">
+        <v>0.642041127189642</v>
+      </c>
+      <c r="G113" t="n">
+        <v>0.4730639730639731</v>
+      </c>
+      <c r="H113" t="n">
+        <v>3279</v>
+      </c>
+      <c r="I113" t="n">
+        <v>1408</v>
+      </c>
+      <c r="J113" t="n">
+        <v>470</v>
+      </c>
+      <c r="K113" t="n">
+        <v>843</v>
+      </c>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="n">
+        <v>0.04083895683288574</v>
+      </c>
+      <c r="N113" t="n">
+        <v>108.3506938566066</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Internal_balanced</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>100</v>
+      </c>
+      <c r="C114" t="inlineStr"/>
+      <c r="D114" t="n">
+        <v>0.6905</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0.3787878787878788</v>
+      </c>
+      <c r="F114" t="n">
+        <v>0.6473724295506473</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0.4779308405960079</v>
+      </c>
+      <c r="H114" t="n">
+        <v>3293</v>
+      </c>
+      <c r="I114" t="n">
+        <v>1394</v>
+      </c>
+      <c r="J114" t="n">
+        <v>463</v>
+      </c>
+      <c r="K114" t="n">
+        <v>850</v>
+      </c>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="n">
+        <v>0.03110289573669434</v>
+      </c>
+      <c r="N114" t="n">
+        <v>108.3506938566066</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>0</v>
+      </c>
+      <c r="C115" t="inlineStr"/>
+      <c r="D115" t="n">
+        <v>0.8108333333333333</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0.6977777777777778</v>
+      </c>
+      <c r="F115" t="n">
+        <v>0.2391469916222392</v>
+      </c>
+      <c r="G115" t="n">
+        <v>0.3562110039705048</v>
+      </c>
+      <c r="H115" t="n">
+        <v>4551</v>
+      </c>
+      <c r="I115" t="n">
+        <v>136</v>
+      </c>
+      <c r="J115" t="n">
+        <v>999</v>
+      </c>
+      <c r="K115" t="n">
+        <v>314</v>
+      </c>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Original_hpt</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>0</v>
+      </c>
+      <c r="C116" t="inlineStr"/>
+      <c r="D116" t="n">
+        <v>0.8102083333333333</v>
+      </c>
+      <c r="E116" t="n">
+        <v>0.7126792406855361</v>
+      </c>
+      <c r="F116" t="n">
+        <v>0.24253022330686</v>
+      </c>
+      <c r="G116" t="n">
+        <v>0.3614996034679863</v>
+      </c>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="n">
+        <v>100</v>
+      </c>
+      <c r="M116" t="n">
+        <v>2.389151096343994</v>
+      </c>
+      <c r="N116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C117" t="inlineStr"/>
+      <c r="D117" t="n">
+        <v>0.7811666666666667</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" t="n">
+        <v>4687</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" t="n">
+        <v>1313</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Input_hpt</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C118" t="inlineStr"/>
+      <c r="D118" t="n">
+        <v>0.7782083333333334</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.209392786026001</v>
+      </c>
+      <c r="N118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>1</v>
+      </c>
+      <c r="C119" t="inlineStr"/>
+      <c r="D119" t="n">
+        <v>0.7811666666666667</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" t="n">
+        <v>4687</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" t="n">
+        <v>1313</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0</v>
+      </c>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Input_hpt</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>1</v>
+      </c>
+      <c r="C120" t="inlineStr"/>
+      <c r="D120" t="n">
+        <v>0.7782083333333334</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.201347827911377</v>
+      </c>
+      <c r="N120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>5</v>
+      </c>
+      <c r="C121" t="inlineStr"/>
+      <c r="D121" t="n">
+        <v>0.7831666666666667</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.02132520944402132</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.04126750184229919</v>
+      </c>
+      <c r="H121" t="n">
+        <v>4671</v>
+      </c>
+      <c r="I121" t="n">
+        <v>16</v>
+      </c>
+      <c r="J121" t="n">
+        <v>1285</v>
+      </c>
+      <c r="K121" t="n">
+        <v>28</v>
+      </c>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Input_hpt</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>5</v>
+      </c>
+      <c r="C122" t="inlineStr"/>
+      <c r="D122" t="n">
+        <v>0.7809583333333333</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.5783236383389382</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.04471391894370071</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.08297648756437934</v>
+      </c>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="n">
+        <v>100</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.2046010494232178</v>
+      </c>
+      <c r="N122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>10</v>
+      </c>
+      <c r="C123" t="inlineStr"/>
+      <c r="D123" t="n">
+        <v>0.7961666666666667</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.67578125</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.1317593297791318</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.2205226258763544</v>
+      </c>
+      <c r="H123" t="n">
+        <v>4604</v>
+      </c>
+      <c r="I123" t="n">
+        <v>83</v>
+      </c>
+      <c r="J123" t="n">
+        <v>1140</v>
+      </c>
+      <c r="K123" t="n">
+        <v>173</v>
+      </c>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Input_hpt</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>10</v>
+      </c>
+      <c r="C124" t="inlineStr"/>
+      <c r="D124" t="n">
+        <v>0.7909166666666667</v>
+      </c>
+      <c r="E124" t="n">
+        <v>0.6520083336347747</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.1232419698401727</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.2072479500188648</v>
+      </c>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.2089660167694092</v>
+      </c>
+      <c r="N124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>30</v>
+      </c>
+      <c r="C125" t="inlineStr"/>
+      <c r="D125" t="n">
+        <v>0.8106666666666666</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.6911447084233261</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.2437166793602437</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.3603603603603603</v>
+      </c>
+      <c r="H125" t="n">
+        <v>4544</v>
+      </c>
+      <c r="I125" t="n">
+        <v>143</v>
+      </c>
+      <c r="J125" t="n">
+        <v>993</v>
+      </c>
+      <c r="K125" t="n">
+        <v>320</v>
+      </c>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Input_hpt</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>30</v>
+      </c>
+      <c r="C126" t="inlineStr"/>
+      <c r="D126" t="n">
+        <v>0.8052499999999998</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0.6937228380734474</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.2188576506933375</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.332430360332738</v>
+      </c>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="n">
+        <v>1</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.2355618476867676</v>
+      </c>
+      <c r="N126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>50</v>
+      </c>
+      <c r="C127" t="inlineStr"/>
+      <c r="D127" t="n">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.6916488222698073</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.246001523229246</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.3629213483146068</v>
+      </c>
+      <c r="H127" t="n">
+        <v>4543</v>
+      </c>
+      <c r="I127" t="n">
+        <v>144</v>
+      </c>
+      <c r="J127" t="n">
+        <v>990</v>
+      </c>
+      <c r="K127" t="n">
+        <v>323</v>
+      </c>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Input_hpt</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>50</v>
+      </c>
+      <c r="C128" t="inlineStr"/>
+      <c r="D128" t="n">
+        <v>0.8083333333333333</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.7104435415548893</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.2314452877033108</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.3487893215793864</v>
+      </c>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="n">
+        <v>1</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.258202075958252</v>
+      </c>
+      <c r="N128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>100</v>
+      </c>
+      <c r="C129" t="inlineStr"/>
+      <c r="D129" t="n">
+        <v>0.8113333333333334</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.6937901498929336</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.2467631378522468</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.3640449438202247</v>
+      </c>
+      <c r="H129" t="n">
+        <v>4544</v>
+      </c>
+      <c r="I129" t="n">
+        <v>143</v>
+      </c>
+      <c r="J129" t="n">
+        <v>989</v>
+      </c>
+      <c r="K129" t="n">
+        <v>324</v>
+      </c>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Input_hpt</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>100</v>
+      </c>
+      <c r="C130" t="inlineStr"/>
+      <c r="D130" t="n">
+        <v>0.810125</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.7142392384934356</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.2406515820508119</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.3595968749758223</v>
+      </c>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="n">
+        <v>1</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.2623648643493652</v>
+      </c>
+      <c r="N130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C131" t="inlineStr"/>
+      <c r="D131" t="n">
+        <v>0.8105</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.6973094170403588</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.2368621477532369</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.3536100056850483</v>
+      </c>
+      <c r="H131" t="n">
+        <v>4552</v>
+      </c>
+      <c r="I131" t="n">
+        <v>135</v>
+      </c>
+      <c r="J131" t="n">
+        <v>1002</v>
+      </c>
+      <c r="K131" t="n">
+        <v>311</v>
+      </c>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>1</v>
+      </c>
+      <c r="C132" t="inlineStr"/>
+      <c r="D132" t="n">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.6984478935698448</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.2399086062452399</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.3571428571428572</v>
+      </c>
+      <c r="H132" t="n">
+        <v>4551</v>
+      </c>
+      <c r="I132" t="n">
+        <v>136</v>
+      </c>
+      <c r="J132" t="n">
+        <v>998</v>
+      </c>
+      <c r="K132" t="n">
+        <v>315</v>
+      </c>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>5</v>
+      </c>
+      <c r="C133" t="inlineStr"/>
+      <c r="D133" t="n">
+        <v>0.8108333333333333</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.6977777777777778</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.2391469916222392</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.3562110039705048</v>
+      </c>
+      <c r="H133" t="n">
+        <v>4551</v>
+      </c>
+      <c r="I133" t="n">
+        <v>136</v>
+      </c>
+      <c r="J133" t="n">
+        <v>999</v>
+      </c>
+      <c r="K133" t="n">
+        <v>314</v>
+      </c>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>10</v>
+      </c>
+      <c r="C134" t="inlineStr"/>
+      <c r="D134" t="n">
+        <v>0.8108333333333333</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.6977777777777778</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.2391469916222392</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.3562110039705048</v>
+      </c>
+      <c r="H134" t="n">
+        <v>4551</v>
+      </c>
+      <c r="I134" t="n">
+        <v>136</v>
+      </c>
+      <c r="J134" t="n">
+        <v>999</v>
+      </c>
+      <c r="K134" t="n">
+        <v>314</v>
+      </c>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>30</v>
+      </c>
+      <c r="C135" t="inlineStr"/>
+      <c r="D135" t="n">
+        <v>0.8108333333333333</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.6977777777777778</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.2391469916222392</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.3562110039705048</v>
+      </c>
+      <c r="H135" t="n">
+        <v>4551</v>
+      </c>
+      <c r="I135" t="n">
+        <v>136</v>
+      </c>
+      <c r="J135" t="n">
+        <v>999</v>
+      </c>
+      <c r="K135" t="n">
+        <v>314</v>
+      </c>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>50</v>
+      </c>
+      <c r="C136" t="inlineStr"/>
+      <c r="D136" t="n">
+        <v>0.8108333333333333</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.6977777777777778</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.2391469916222392</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.3562110039705048</v>
+      </c>
+      <c r="H136" t="n">
+        <v>4551</v>
+      </c>
+      <c r="I136" t="n">
+        <v>136</v>
+      </c>
+      <c r="J136" t="n">
+        <v>999</v>
+      </c>
+      <c r="K136" t="n">
+        <v>314</v>
+      </c>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>100</v>
+      </c>
+      <c r="C137" t="inlineStr"/>
+      <c r="D137" t="n">
+        <v>0.8108333333333333</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.6977777777777778</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.2391469916222392</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.3562110039705048</v>
+      </c>
+      <c r="H137" t="n">
+        <v>4551</v>
+      </c>
+      <c r="I137" t="n">
+        <v>136</v>
+      </c>
+      <c r="J137" t="n">
+        <v>999</v>
+      </c>
+      <c r="K137" t="n">
+        <v>314</v>
+      </c>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C138" t="inlineStr"/>
+      <c r="D138" t="n">
+        <v>0.6264999999999999</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.2433628318584071</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.3351104341203351</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.2819609099647549</v>
+      </c>
+      <c r="H138" t="n">
+        <v>3319</v>
+      </c>
+      <c r="I138" t="n">
+        <v>1368</v>
+      </c>
+      <c r="J138" t="n">
+        <v>873</v>
+      </c>
+      <c r="K138" t="n">
+        <v>440</v>
+      </c>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="n">
+        <v>0.006972789764404297</v>
+      </c>
+      <c r="N138" t="n">
+        <v>94.59893444466807</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>1</v>
+      </c>
+      <c r="C139" t="inlineStr"/>
+      <c r="D139" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.3087195600942655</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.2993145468392993</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.3039443155452436</v>
+      </c>
+      <c r="H139" t="n">
+        <v>3807</v>
+      </c>
+      <c r="I139" t="n">
+        <v>880</v>
+      </c>
+      <c r="J139" t="n">
+        <v>920</v>
+      </c>
+      <c r="K139" t="n">
+        <v>393</v>
+      </c>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="n">
+        <v>0.009835004806518555</v>
+      </c>
+      <c r="N139" t="n">
+        <v>94.59893444466807</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>5</v>
+      </c>
+      <c r="C140" t="inlineStr"/>
+      <c r="D140" t="n">
+        <v>0.7495000000000001</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.3962882096069869</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.2764661081492765</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.3257065948855989</v>
+      </c>
+      <c r="H140" t="n">
+        <v>4134</v>
+      </c>
+      <c r="I140" t="n">
+        <v>553</v>
+      </c>
+      <c r="J140" t="n">
+        <v>950</v>
+      </c>
+      <c r="K140" t="n">
+        <v>363</v>
+      </c>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="n">
+        <v>0.03328371047973633</v>
+      </c>
+      <c r="N140" t="n">
+        <v>94.59893444466807</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>10</v>
+      </c>
+      <c r="C141" t="inlineStr"/>
+      <c r="D141" t="n">
+        <v>0.7448333333333333</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.3892276422764228</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.2916984006092917</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.3334784501523727</v>
+      </c>
+      <c r="H141" t="n">
+        <v>4086</v>
+      </c>
+      <c r="I141" t="n">
+        <v>601</v>
+      </c>
+      <c r="J141" t="n">
+        <v>930</v>
+      </c>
+      <c r="K141" t="n">
+        <v>383</v>
+      </c>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="n">
+        <v>0.06246709823608398</v>
+      </c>
+      <c r="N141" t="n">
+        <v>94.59893444466807</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>30</v>
+      </c>
+      <c r="C142" t="inlineStr"/>
+      <c r="D142" t="n">
+        <v>0.8038333333333333</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.6422594142259415</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.2338156892612338</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.3428252372975991</v>
+      </c>
+      <c r="H142" t="n">
+        <v>4516</v>
+      </c>
+      <c r="I142" t="n">
+        <v>171</v>
+      </c>
+      <c r="J142" t="n">
+        <v>1006</v>
+      </c>
+      <c r="K142" t="n">
+        <v>307</v>
+      </c>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="n">
+        <v>0.05238914489746094</v>
+      </c>
+      <c r="N142" t="n">
+        <v>94.59893444466807</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>50</v>
+      </c>
+      <c r="C143" t="inlineStr"/>
+      <c r="D143" t="n">
+        <v>0.8075</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.6763392857142857</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.2307692307692308</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.3441226575809199</v>
+      </c>
+      <c r="H143" t="n">
+        <v>4542</v>
+      </c>
+      <c r="I143" t="n">
+        <v>145</v>
+      </c>
+      <c r="J143" t="n">
+        <v>1010</v>
+      </c>
+      <c r="K143" t="n">
+        <v>303</v>
+      </c>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="n">
+        <v>0.03848814964294434</v>
+      </c>
+      <c r="N143" t="n">
+        <v>94.59893444466807</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>100</v>
+      </c>
+      <c r="C144" t="inlineStr"/>
+      <c r="D144" t="n">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="E144" t="n">
+        <v>0.7038724373576309</v>
+      </c>
+      <c r="F144" t="n">
+        <v>0.2353389185072353</v>
+      </c>
+      <c r="G144" t="n">
+        <v>0.3527397260273973</v>
+      </c>
+      <c r="H144" t="n">
+        <v>4557</v>
+      </c>
+      <c r="I144" t="n">
+        <v>130</v>
+      </c>
+      <c r="J144" t="n">
+        <v>1004</v>
+      </c>
+      <c r="K144" t="n">
+        <v>309</v>
+      </c>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="n">
+        <v>0.01766300201416016</v>
+      </c>
+      <c r="N144" t="n">
+        <v>94.59893444466807</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results/model_results_cc.xlsx
+++ b/results/model_results_cc.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N144"/>
+  <dimension ref="A1:N174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5874,6 +5874,1142 @@
         <v>94.59893444466807</v>
       </c>
     </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>0</v>
+      </c>
+      <c r="C145" t="inlineStr"/>
+      <c r="D145" t="n">
+        <v>0.8108333333333333</v>
+      </c>
+      <c r="E145" t="n">
+        <v>0.6977777777777778</v>
+      </c>
+      <c r="F145" t="n">
+        <v>0.2391469916222392</v>
+      </c>
+      <c r="G145" t="n">
+        <v>0.3562110039705048</v>
+      </c>
+      <c r="H145" t="n">
+        <v>4551</v>
+      </c>
+      <c r="I145" t="n">
+        <v>136</v>
+      </c>
+      <c r="J145" t="n">
+        <v>999</v>
+      </c>
+      <c r="K145" t="n">
+        <v>314</v>
+      </c>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr"/>
+      <c r="N145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Original_hpt</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>0</v>
+      </c>
+      <c r="C146" t="inlineStr"/>
+      <c r="D146" t="n">
+        <v>0.8102083333333333</v>
+      </c>
+      <c r="E146" t="n">
+        <v>0.7126792406855361</v>
+      </c>
+      <c r="F146" t="n">
+        <v>0.24253022330686</v>
+      </c>
+      <c r="G146" t="n">
+        <v>0.3614996034679863</v>
+      </c>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="n">
+        <v>100</v>
+      </c>
+      <c r="M146" t="n">
+        <v>2.09797191619873</v>
+      </c>
+      <c r="N146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C147" t="inlineStr"/>
+      <c r="D147" t="n">
+        <v>0.7811666666666667</v>
+      </c>
+      <c r="E147" t="n">
+        <v>0</v>
+      </c>
+      <c r="F147" t="n">
+        <v>0</v>
+      </c>
+      <c r="G147" t="n">
+        <v>0</v>
+      </c>
+      <c r="H147" t="n">
+        <v>4687</v>
+      </c>
+      <c r="I147" t="n">
+        <v>0</v>
+      </c>
+      <c r="J147" t="n">
+        <v>1313</v>
+      </c>
+      <c r="K147" t="n">
+        <v>0</v>
+      </c>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Input_hpt</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C148" t="inlineStr"/>
+      <c r="D148" t="n">
+        <v>0.7782083333333334</v>
+      </c>
+      <c r="E148" t="n">
+        <v>0</v>
+      </c>
+      <c r="F148" t="n">
+        <v>0</v>
+      </c>
+      <c r="G148" t="n">
+        <v>0</v>
+      </c>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M148" t="n">
+        <v>0.2185850143432617</v>
+      </c>
+      <c r="N148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>1</v>
+      </c>
+      <c r="C149" t="inlineStr"/>
+      <c r="D149" t="n">
+        <v>0.7811666666666667</v>
+      </c>
+      <c r="E149" t="n">
+        <v>0</v>
+      </c>
+      <c r="F149" t="n">
+        <v>0</v>
+      </c>
+      <c r="G149" t="n">
+        <v>0</v>
+      </c>
+      <c r="H149" t="n">
+        <v>4687</v>
+      </c>
+      <c r="I149" t="n">
+        <v>0</v>
+      </c>
+      <c r="J149" t="n">
+        <v>1313</v>
+      </c>
+      <c r="K149" t="n">
+        <v>0</v>
+      </c>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Input_hpt</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>1</v>
+      </c>
+      <c r="C150" t="inlineStr"/>
+      <c r="D150" t="n">
+        <v>0.7782083333333334</v>
+      </c>
+      <c r="E150" t="n">
+        <v>0</v>
+      </c>
+      <c r="F150" t="n">
+        <v>0</v>
+      </c>
+      <c r="G150" t="n">
+        <v>0</v>
+      </c>
+      <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M150" t="n">
+        <v>0.2036879062652588</v>
+      </c>
+      <c r="N150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>5</v>
+      </c>
+      <c r="C151" t="inlineStr"/>
+      <c r="D151" t="n">
+        <v>0.7831666666666667</v>
+      </c>
+      <c r="E151" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="F151" t="n">
+        <v>0.02132520944402132</v>
+      </c>
+      <c r="G151" t="n">
+        <v>0.04126750184229919</v>
+      </c>
+      <c r="H151" t="n">
+        <v>4671</v>
+      </c>
+      <c r="I151" t="n">
+        <v>16</v>
+      </c>
+      <c r="J151" t="n">
+        <v>1285</v>
+      </c>
+      <c r="K151" t="n">
+        <v>28</v>
+      </c>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Input_hpt</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>5</v>
+      </c>
+      <c r="C152" t="inlineStr"/>
+      <c r="D152" t="n">
+        <v>0.7809583333333333</v>
+      </c>
+      <c r="E152" t="n">
+        <v>0.5783236383389382</v>
+      </c>
+      <c r="F152" t="n">
+        <v>0.04471391894370071</v>
+      </c>
+      <c r="G152" t="n">
+        <v>0.08297648756437934</v>
+      </c>
+      <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="n">
+        <v>100</v>
+      </c>
+      <c r="M152" t="n">
+        <v>0.2065608501434326</v>
+      </c>
+      <c r="N152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>10</v>
+      </c>
+      <c r="C153" t="inlineStr"/>
+      <c r="D153" t="n">
+        <v>0.7961666666666667</v>
+      </c>
+      <c r="E153" t="n">
+        <v>0.67578125</v>
+      </c>
+      <c r="F153" t="n">
+        <v>0.1317593297791318</v>
+      </c>
+      <c r="G153" t="n">
+        <v>0.2205226258763544</v>
+      </c>
+      <c r="H153" t="n">
+        <v>4604</v>
+      </c>
+      <c r="I153" t="n">
+        <v>83</v>
+      </c>
+      <c r="J153" t="n">
+        <v>1140</v>
+      </c>
+      <c r="K153" t="n">
+        <v>173</v>
+      </c>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" t="inlineStr"/>
+      <c r="N153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Input_hpt</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>10</v>
+      </c>
+      <c r="C154" t="inlineStr"/>
+      <c r="D154" t="n">
+        <v>0.7909166666666667</v>
+      </c>
+      <c r="E154" t="n">
+        <v>0.6520083336347747</v>
+      </c>
+      <c r="F154" t="n">
+        <v>0.1232419698401727</v>
+      </c>
+      <c r="G154" t="n">
+        <v>0.2072479500188648</v>
+      </c>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M154" t="n">
+        <v>0.20932936668396</v>
+      </c>
+      <c r="N154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>30</v>
+      </c>
+      <c r="C155" t="inlineStr"/>
+      <c r="D155" t="n">
+        <v>0.8106666666666666</v>
+      </c>
+      <c r="E155" t="n">
+        <v>0.6911447084233261</v>
+      </c>
+      <c r="F155" t="n">
+        <v>0.2437166793602437</v>
+      </c>
+      <c r="G155" t="n">
+        <v>0.3603603603603603</v>
+      </c>
+      <c r="H155" t="n">
+        <v>4544</v>
+      </c>
+      <c r="I155" t="n">
+        <v>143</v>
+      </c>
+      <c r="J155" t="n">
+        <v>993</v>
+      </c>
+      <c r="K155" t="n">
+        <v>320</v>
+      </c>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="inlineStr"/>
+      <c r="N155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Input_hpt</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>30</v>
+      </c>
+      <c r="C156" t="inlineStr"/>
+      <c r="D156" t="n">
+        <v>0.8052499999999998</v>
+      </c>
+      <c r="E156" t="n">
+        <v>0.6937228380734474</v>
+      </c>
+      <c r="F156" t="n">
+        <v>0.2188576506933375</v>
+      </c>
+      <c r="G156" t="n">
+        <v>0.332430360332738</v>
+      </c>
+      <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="n">
+        <v>1</v>
+      </c>
+      <c r="M156" t="n">
+        <v>0.2514088153839111</v>
+      </c>
+      <c r="N156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>50</v>
+      </c>
+      <c r="C157" t="inlineStr"/>
+      <c r="D157" t="n">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="E157" t="n">
+        <v>0.6916488222698073</v>
+      </c>
+      <c r="F157" t="n">
+        <v>0.246001523229246</v>
+      </c>
+      <c r="G157" t="n">
+        <v>0.3629213483146068</v>
+      </c>
+      <c r="H157" t="n">
+        <v>4543</v>
+      </c>
+      <c r="I157" t="n">
+        <v>144</v>
+      </c>
+      <c r="J157" t="n">
+        <v>990</v>
+      </c>
+      <c r="K157" t="n">
+        <v>323</v>
+      </c>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr"/>
+      <c r="N157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Input_hpt</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>50</v>
+      </c>
+      <c r="C158" t="inlineStr"/>
+      <c r="D158" t="n">
+        <v>0.8083333333333333</v>
+      </c>
+      <c r="E158" t="n">
+        <v>0.7104435415548893</v>
+      </c>
+      <c r="F158" t="n">
+        <v>0.2314452877033108</v>
+      </c>
+      <c r="G158" t="n">
+        <v>0.3487893215793864</v>
+      </c>
+      <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="n">
+        <v>1</v>
+      </c>
+      <c r="M158" t="n">
+        <v>0.2744681835174561</v>
+      </c>
+      <c r="N158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>100</v>
+      </c>
+      <c r="C159" t="inlineStr"/>
+      <c r="D159" t="n">
+        <v>0.8113333333333334</v>
+      </c>
+      <c r="E159" t="n">
+        <v>0.6937901498929336</v>
+      </c>
+      <c r="F159" t="n">
+        <v>0.2467631378522468</v>
+      </c>
+      <c r="G159" t="n">
+        <v>0.3640449438202247</v>
+      </c>
+      <c r="H159" t="n">
+        <v>4544</v>
+      </c>
+      <c r="I159" t="n">
+        <v>143</v>
+      </c>
+      <c r="J159" t="n">
+        <v>989</v>
+      </c>
+      <c r="K159" t="n">
+        <v>324</v>
+      </c>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" t="inlineStr"/>
+      <c r="N159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Input_hpt</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>100</v>
+      </c>
+      <c r="C160" t="inlineStr"/>
+      <c r="D160" t="n">
+        <v>0.810125</v>
+      </c>
+      <c r="E160" t="n">
+        <v>0.7142392384934356</v>
+      </c>
+      <c r="F160" t="n">
+        <v>0.2406515820508119</v>
+      </c>
+      <c r="G160" t="n">
+        <v>0.3595968749758223</v>
+      </c>
+      <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="n">
+        <v>1</v>
+      </c>
+      <c r="M160" t="n">
+        <v>0.2765541076660156</v>
+      </c>
+      <c r="N160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C161" t="inlineStr"/>
+      <c r="D161" t="n">
+        <v>0.8105</v>
+      </c>
+      <c r="E161" t="n">
+        <v>0.6973094170403588</v>
+      </c>
+      <c r="F161" t="n">
+        <v>0.2368621477532369</v>
+      </c>
+      <c r="G161" t="n">
+        <v>0.3536100056850483</v>
+      </c>
+      <c r="H161" t="n">
+        <v>4552</v>
+      </c>
+      <c r="I161" t="n">
+        <v>135</v>
+      </c>
+      <c r="J161" t="n">
+        <v>1002</v>
+      </c>
+      <c r="K161" t="n">
+        <v>311</v>
+      </c>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>1</v>
+      </c>
+      <c r="C162" t="inlineStr"/>
+      <c r="D162" t="n">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="E162" t="n">
+        <v>0.6984478935698448</v>
+      </c>
+      <c r="F162" t="n">
+        <v>0.2399086062452399</v>
+      </c>
+      <c r="G162" t="n">
+        <v>0.3571428571428572</v>
+      </c>
+      <c r="H162" t="n">
+        <v>4551</v>
+      </c>
+      <c r="I162" t="n">
+        <v>136</v>
+      </c>
+      <c r="J162" t="n">
+        <v>998</v>
+      </c>
+      <c r="K162" t="n">
+        <v>315</v>
+      </c>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" t="inlineStr"/>
+      <c r="N162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>5</v>
+      </c>
+      <c r="C163" t="inlineStr"/>
+      <c r="D163" t="n">
+        <v>0.8108333333333333</v>
+      </c>
+      <c r="E163" t="n">
+        <v>0.6977777777777778</v>
+      </c>
+      <c r="F163" t="n">
+        <v>0.2391469916222392</v>
+      </c>
+      <c r="G163" t="n">
+        <v>0.3562110039705048</v>
+      </c>
+      <c r="H163" t="n">
+        <v>4551</v>
+      </c>
+      <c r="I163" t="n">
+        <v>136</v>
+      </c>
+      <c r="J163" t="n">
+        <v>999</v>
+      </c>
+      <c r="K163" t="n">
+        <v>314</v>
+      </c>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" t="inlineStr"/>
+      <c r="N163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>10</v>
+      </c>
+      <c r="C164" t="inlineStr"/>
+      <c r="D164" t="n">
+        <v>0.8108333333333333</v>
+      </c>
+      <c r="E164" t="n">
+        <v>0.6977777777777778</v>
+      </c>
+      <c r="F164" t="n">
+        <v>0.2391469916222392</v>
+      </c>
+      <c r="G164" t="n">
+        <v>0.3562110039705048</v>
+      </c>
+      <c r="H164" t="n">
+        <v>4551</v>
+      </c>
+      <c r="I164" t="n">
+        <v>136</v>
+      </c>
+      <c r="J164" t="n">
+        <v>999</v>
+      </c>
+      <c r="K164" t="n">
+        <v>314</v>
+      </c>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>30</v>
+      </c>
+      <c r="C165" t="inlineStr"/>
+      <c r="D165" t="n">
+        <v>0.8108333333333333</v>
+      </c>
+      <c r="E165" t="n">
+        <v>0.6977777777777778</v>
+      </c>
+      <c r="F165" t="n">
+        <v>0.2391469916222392</v>
+      </c>
+      <c r="G165" t="n">
+        <v>0.3562110039705048</v>
+      </c>
+      <c r="H165" t="n">
+        <v>4551</v>
+      </c>
+      <c r="I165" t="n">
+        <v>136</v>
+      </c>
+      <c r="J165" t="n">
+        <v>999</v>
+      </c>
+      <c r="K165" t="n">
+        <v>314</v>
+      </c>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" t="inlineStr"/>
+      <c r="N165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>50</v>
+      </c>
+      <c r="C166" t="inlineStr"/>
+      <c r="D166" t="n">
+        <v>0.8108333333333333</v>
+      </c>
+      <c r="E166" t="n">
+        <v>0.6977777777777778</v>
+      </c>
+      <c r="F166" t="n">
+        <v>0.2391469916222392</v>
+      </c>
+      <c r="G166" t="n">
+        <v>0.3562110039705048</v>
+      </c>
+      <c r="H166" t="n">
+        <v>4551</v>
+      </c>
+      <c r="I166" t="n">
+        <v>136</v>
+      </c>
+      <c r="J166" t="n">
+        <v>999</v>
+      </c>
+      <c r="K166" t="n">
+        <v>314</v>
+      </c>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" t="inlineStr"/>
+      <c r="N166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>100</v>
+      </c>
+      <c r="C167" t="inlineStr"/>
+      <c r="D167" t="n">
+        <v>0.8108333333333333</v>
+      </c>
+      <c r="E167" t="n">
+        <v>0.6977777777777778</v>
+      </c>
+      <c r="F167" t="n">
+        <v>0.2391469916222392</v>
+      </c>
+      <c r="G167" t="n">
+        <v>0.3562110039705048</v>
+      </c>
+      <c r="H167" t="n">
+        <v>4551</v>
+      </c>
+      <c r="I167" t="n">
+        <v>136</v>
+      </c>
+      <c r="J167" t="n">
+        <v>999</v>
+      </c>
+      <c r="K167" t="n">
+        <v>314</v>
+      </c>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" t="inlineStr"/>
+      <c r="N167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C168" t="inlineStr"/>
+      <c r="D168" t="n">
+        <v>0.6264999999999999</v>
+      </c>
+      <c r="E168" t="n">
+        <v>0.2433628318584071</v>
+      </c>
+      <c r="F168" t="n">
+        <v>0.3351104341203351</v>
+      </c>
+      <c r="G168" t="n">
+        <v>0.2819609099647549</v>
+      </c>
+      <c r="H168" t="n">
+        <v>3319</v>
+      </c>
+      <c r="I168" t="n">
+        <v>1368</v>
+      </c>
+      <c r="J168" t="n">
+        <v>873</v>
+      </c>
+      <c r="K168" t="n">
+        <v>440</v>
+      </c>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" t="n">
+        <v>0.00569605827331543</v>
+      </c>
+      <c r="N168" t="n">
+        <v>94.59893444466807</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>1</v>
+      </c>
+      <c r="C169" t="inlineStr"/>
+      <c r="D169" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E169" t="n">
+        <v>0.3087195600942655</v>
+      </c>
+      <c r="F169" t="n">
+        <v>0.2993145468392993</v>
+      </c>
+      <c r="G169" t="n">
+        <v>0.3039443155452436</v>
+      </c>
+      <c r="H169" t="n">
+        <v>3807</v>
+      </c>
+      <c r="I169" t="n">
+        <v>880</v>
+      </c>
+      <c r="J169" t="n">
+        <v>920</v>
+      </c>
+      <c r="K169" t="n">
+        <v>393</v>
+      </c>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" t="n">
+        <v>0.008444309234619141</v>
+      </c>
+      <c r="N169" t="n">
+        <v>94.59893444466807</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>5</v>
+      </c>
+      <c r="C170" t="inlineStr"/>
+      <c r="D170" t="n">
+        <v>0.7495000000000001</v>
+      </c>
+      <c r="E170" t="n">
+        <v>0.3962882096069869</v>
+      </c>
+      <c r="F170" t="n">
+        <v>0.2764661081492765</v>
+      </c>
+      <c r="G170" t="n">
+        <v>0.3257065948855989</v>
+      </c>
+      <c r="H170" t="n">
+        <v>4134</v>
+      </c>
+      <c r="I170" t="n">
+        <v>553</v>
+      </c>
+      <c r="J170" t="n">
+        <v>950</v>
+      </c>
+      <c r="K170" t="n">
+        <v>363</v>
+      </c>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" t="n">
+        <v>0.03297305107116699</v>
+      </c>
+      <c r="N170" t="n">
+        <v>94.59893444466807</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>10</v>
+      </c>
+      <c r="C171" t="inlineStr"/>
+      <c r="D171" t="n">
+        <v>0.7448333333333333</v>
+      </c>
+      <c r="E171" t="n">
+        <v>0.3892276422764228</v>
+      </c>
+      <c r="F171" t="n">
+        <v>0.2916984006092917</v>
+      </c>
+      <c r="G171" t="n">
+        <v>0.3334784501523727</v>
+      </c>
+      <c r="H171" t="n">
+        <v>4086</v>
+      </c>
+      <c r="I171" t="n">
+        <v>601</v>
+      </c>
+      <c r="J171" t="n">
+        <v>930</v>
+      </c>
+      <c r="K171" t="n">
+        <v>383</v>
+      </c>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" t="n">
+        <v>0.06309103965759277</v>
+      </c>
+      <c r="N171" t="n">
+        <v>94.59893444466807</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>30</v>
+      </c>
+      <c r="C172" t="inlineStr"/>
+      <c r="D172" t="n">
+        <v>0.8038333333333333</v>
+      </c>
+      <c r="E172" t="n">
+        <v>0.6422594142259415</v>
+      </c>
+      <c r="F172" t="n">
+        <v>0.2338156892612338</v>
+      </c>
+      <c r="G172" t="n">
+        <v>0.3428252372975991</v>
+      </c>
+      <c r="H172" t="n">
+        <v>4516</v>
+      </c>
+      <c r="I172" t="n">
+        <v>171</v>
+      </c>
+      <c r="J172" t="n">
+        <v>1006</v>
+      </c>
+      <c r="K172" t="n">
+        <v>307</v>
+      </c>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" t="n">
+        <v>0.05076909065246582</v>
+      </c>
+      <c r="N172" t="n">
+        <v>94.59893444466807</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>50</v>
+      </c>
+      <c r="C173" t="inlineStr"/>
+      <c r="D173" t="n">
+        <v>0.8075</v>
+      </c>
+      <c r="E173" t="n">
+        <v>0.6763392857142857</v>
+      </c>
+      <c r="F173" t="n">
+        <v>0.2307692307692308</v>
+      </c>
+      <c r="G173" t="n">
+        <v>0.3441226575809199</v>
+      </c>
+      <c r="H173" t="n">
+        <v>4542</v>
+      </c>
+      <c r="I173" t="n">
+        <v>145</v>
+      </c>
+      <c r="J173" t="n">
+        <v>1010</v>
+      </c>
+      <c r="K173" t="n">
+        <v>303</v>
+      </c>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" t="n">
+        <v>0.03680515289306641</v>
+      </c>
+      <c r="N173" t="n">
+        <v>94.59893444466807</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>100</v>
+      </c>
+      <c r="C174" t="inlineStr"/>
+      <c r="D174" t="n">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="E174" t="n">
+        <v>0.7038724373576309</v>
+      </c>
+      <c r="F174" t="n">
+        <v>0.2353389185072353</v>
+      </c>
+      <c r="G174" t="n">
+        <v>0.3527397260273973</v>
+      </c>
+      <c r="H174" t="n">
+        <v>4557</v>
+      </c>
+      <c r="I174" t="n">
+        <v>130</v>
+      </c>
+      <c r="J174" t="n">
+        <v>1004</v>
+      </c>
+      <c r="K174" t="n">
+        <v>309</v>
+      </c>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" t="n">
+        <v>0.01731204986572266</v>
+      </c>
+      <c r="N174" t="n">
+        <v>94.59893444466807</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
